--- a/reports/Debug-snowbowl-20260105/snowbowl_Report_20260105.xlsx
+++ b/reports/Debug-snowbowl-20260105/snowbowl_Report_20260105.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>snowbowl Resort
 Daily Management Report
@@ -98,15 +98,6 @@
   </si>
   <si>
     <t>FINANCIALS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Payroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR % of </t>
   </si>
   <si>
     <t>Mountain G&amp;A - Revenue</t>
@@ -968,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N180"/>
+  <dimension ref="A1:N177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1123,7 +1114,7 @@
         <v>1945</v>
       </c>
       <c r="L6" s="4">
-        <v>11450</v>
+        <v>11446</v>
       </c>
       <c r="M6" s="4">
         <v>8300</v>
@@ -1211,7 +1202,7 @@
         <v>6321</v>
       </c>
       <c r="L8" s="4">
-        <v>61044</v>
+        <v>61043</v>
       </c>
       <c r="M8" s="4">
         <v>52450</v>
@@ -1255,7 +1246,7 @@
         <v>984</v>
       </c>
       <c r="L9" s="4">
-        <v>11659</v>
+        <v>11656</v>
       </c>
       <c r="M9" s="4">
         <v>0</v>
@@ -1299,7 +1290,7 @@
         <v>15065</v>
       </c>
       <c r="L10" s="4">
-        <v>125796</v>
+        <v>125788</v>
       </c>
       <c r="M10" s="4">
         <v>93575</v>
@@ -1345,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="4">
-        <v>2104.8</v>
+        <v>0</v>
       </c>
       <c r="L13" s="4">
         <v>0</v>
@@ -1354,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>6549.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1365,40 +1356,40 @@
         <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>911.72</v>
       </c>
       <c r="D14" s="4">
-        <v>0</v>
+        <v>897.27</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
       </c>
       <c r="F14" s="4">
-        <v>0</v>
+        <v>6382.04</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>897.27</v>
       </c>
       <c r="H14" s="4">
-        <v>0</v>
+        <v>6280.89</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
       </c>
       <c r="J14" s="4">
-        <v>0</v>
+        <v>4558.6</v>
       </c>
       <c r="K14" s="4">
-        <v>0</v>
+        <v>4486.35</v>
       </c>
       <c r="L14" s="4">
         <v>0</v>
       </c>
       <c r="M14" s="4">
-        <v>0</v>
+        <v>60173.52</v>
       </c>
       <c r="N14" s="4">
-        <v>0</v>
+        <v>59219.82</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1494,43 +1485,43 @@
         <v>27</v>
       </c>
       <c r="B17" s="4">
-        <v>927.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4">
-        <v>911.72</v>
+        <v>5715.51</v>
       </c>
       <c r="D17" s="4">
-        <v>897.27</v>
+        <v>5874.36</v>
       </c>
       <c r="E17" s="4">
-        <v>927.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4">
-        <v>6382.04</v>
+        <v>41053.61</v>
       </c>
       <c r="G17" s="4">
-        <v>897.27</v>
+        <v>5874.36</v>
       </c>
       <c r="H17" s="4">
-        <v>6280.89</v>
+        <v>39842.53</v>
       </c>
       <c r="I17" s="4">
-        <v>4639.7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4">
-        <v>4558.6</v>
+        <v>29101.15</v>
       </c>
       <c r="K17" s="4">
-        <v>4486.35</v>
+        <v>30848.02</v>
       </c>
       <c r="L17" s="4">
-        <v>61244.04</v>
+        <v>850.3859722222222</v>
       </c>
       <c r="M17" s="4">
-        <v>60173.52</v>
+        <v>200880.63</v>
       </c>
       <c r="N17" s="4">
-        <v>59219.82</v>
+        <v>244895.08</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1626,43 +1617,43 @@
         <v>30</v>
       </c>
       <c r="B20" s="4">
-        <v>5297.138625000001</v>
+        <v>0</v>
       </c>
       <c r="C20" s="4">
-        <v>5715.51</v>
+        <v>1155.27</v>
       </c>
       <c r="D20" s="4">
-        <v>5874.36</v>
+        <v>900.3</v>
       </c>
       <c r="E20" s="4">
-        <v>5297.138624999999</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4">
-        <v>41053.61</v>
+        <v>9208.799999999999</v>
       </c>
       <c r="G20" s="4">
-        <v>5874.36</v>
+        <v>900.3</v>
       </c>
       <c r="H20" s="4">
-        <v>39842.53</v>
+        <v>8792.200000000001</v>
       </c>
       <c r="I20" s="4">
-        <v>27446.16511111111</v>
+        <v>1459.958177777778</v>
       </c>
       <c r="J20" s="4">
-        <v>29101.15</v>
+        <v>6714.76</v>
       </c>
       <c r="K20" s="4">
-        <v>30848.02</v>
+        <v>6736.91</v>
       </c>
       <c r="L20" s="4">
-        <v>256413.0466527776</v>
+        <v>17894.51824444444</v>
       </c>
       <c r="M20" s="4">
-        <v>200880.63</v>
+        <v>80054.73</v>
       </c>
       <c r="N20" s="4">
-        <v>244895.08</v>
+        <v>85580.05</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1758,43 +1749,43 @@
         <v>33</v>
       </c>
       <c r="B23" s="4">
-        <v>1288.517388888889</v>
+        <v>190.8397083333333</v>
       </c>
       <c r="C23" s="4">
-        <v>1155.27</v>
+        <v>2725.11</v>
       </c>
       <c r="D23" s="4">
-        <v>900.3</v>
+        <v>2560.33</v>
       </c>
       <c r="E23" s="4">
-        <v>1288.517388888889</v>
+        <v>190.8397083333333</v>
       </c>
       <c r="F23" s="4">
-        <v>9208.799999999999</v>
+        <v>15890.79</v>
       </c>
       <c r="G23" s="4">
-        <v>900.3</v>
+        <v>2560.33</v>
       </c>
       <c r="H23" s="4">
-        <v>8792.200000000001</v>
+        <v>14825.91</v>
       </c>
       <c r="I23" s="4">
-        <v>6089.375094444444</v>
+        <v>190.8397083333333</v>
       </c>
       <c r="J23" s="4">
-        <v>6714.76</v>
+        <v>10440.57</v>
       </c>
       <c r="K23" s="4">
-        <v>6736.91</v>
+        <v>11169.52</v>
       </c>
       <c r="L23" s="4">
-        <v>81280.66135555554</v>
+        <v>882.7871666666667</v>
       </c>
       <c r="M23" s="4">
-        <v>80054.73</v>
+        <v>159306.69</v>
       </c>
       <c r="N23" s="4">
-        <v>85580.05</v>
+        <v>143377.16</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1890,43 +1881,43 @@
         <v>36</v>
       </c>
       <c r="B26" s="4">
-        <v>1691.813069444445</v>
+        <v>177.0521666666667</v>
       </c>
       <c r="C26" s="4">
-        <v>2725.11</v>
+        <v>962.84</v>
       </c>
       <c r="D26" s="4">
-        <v>2560.33</v>
+        <v>779.8200000000001</v>
       </c>
       <c r="E26" s="4">
-        <v>1691.813069444444</v>
+        <v>177.0521666666667</v>
       </c>
       <c r="F26" s="4">
-        <v>15890.79</v>
+        <v>6657.1</v>
       </c>
       <c r="G26" s="4">
-        <v>2560.33</v>
+        <v>779.8200000000001</v>
       </c>
       <c r="H26" s="4">
-        <v>14825.91</v>
+        <v>4284.83</v>
       </c>
       <c r="I26" s="4">
-        <v>7826.911430555553</v>
+        <v>268.0157083333334</v>
       </c>
       <c r="J26" s="4">
-        <v>10440.57</v>
+        <v>3819.64</v>
       </c>
       <c r="K26" s="4">
-        <v>11169.52</v>
+        <v>2937.45</v>
       </c>
       <c r="L26" s="4">
-        <v>166258.9085833335</v>
+        <v>7305.990597222221</v>
       </c>
       <c r="M26" s="4">
-        <v>159306.69</v>
+        <v>31083.68</v>
       </c>
       <c r="N26" s="4">
-        <v>143377.16</v>
+        <v>23928.74</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2022,43 +2013,43 @@
         <v>39</v>
       </c>
       <c r="B29" s="4">
-        <v>517.7535555555555</v>
+        <v>85.09916666666666</v>
       </c>
       <c r="C29" s="4">
-        <v>962.84</v>
+        <v>1450.73</v>
       </c>
       <c r="D29" s="4">
-        <v>779.8200000000001</v>
+        <v>782.04</v>
       </c>
       <c r="E29" s="4">
-        <v>517.7535555555555</v>
+        <v>85.09916666666666</v>
       </c>
       <c r="F29" s="4">
-        <v>6657.1</v>
+        <v>9718.700000000001</v>
       </c>
       <c r="G29" s="4">
-        <v>779.8200000000001</v>
+        <v>782.04</v>
       </c>
       <c r="H29" s="4">
-        <v>4284.83</v>
+        <v>5790.46</v>
       </c>
       <c r="I29" s="4">
-        <v>3608.500291666667</v>
+        <v>210.0869444444444</v>
       </c>
       <c r="J29" s="4">
-        <v>3819.64</v>
+        <v>7027.4</v>
       </c>
       <c r="K29" s="4">
-        <v>2937.45</v>
+        <v>4778.02</v>
       </c>
       <c r="L29" s="4">
-        <v>44800.24975</v>
+        <v>425.1494444444444</v>
       </c>
       <c r="M29" s="4">
-        <v>31083.68</v>
+        <v>65242.23</v>
       </c>
       <c r="N29" s="4">
-        <v>23928.74</v>
+        <v>50299.17</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2154,43 +2145,43 @@
         <v>42</v>
       </c>
       <c r="B32" s="4">
-        <v>296.0936666666666</v>
+        <v>0</v>
       </c>
       <c r="C32" s="4">
-        <v>1450.73</v>
+        <v>760</v>
       </c>
       <c r="D32" s="4">
-        <v>782.04</v>
+        <v>735.7</v>
       </c>
       <c r="E32" s="4">
-        <v>296.0936666666666</v>
+        <v>0</v>
       </c>
       <c r="F32" s="4">
-        <v>9718.700000000001</v>
+        <v>4560</v>
       </c>
       <c r="G32" s="4">
-        <v>782.04</v>
+        <v>735.7</v>
       </c>
       <c r="H32" s="4">
-        <v>5790.46</v>
+        <v>4504.83</v>
       </c>
       <c r="I32" s="4">
-        <v>2622.051402777777</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4">
-        <v>7027.4</v>
+        <v>2685</v>
       </c>
       <c r="K32" s="4">
-        <v>4778.02</v>
+        <v>2770.24</v>
       </c>
       <c r="L32" s="4">
-        <v>42694.42406944445</v>
+        <v>0</v>
       </c>
       <c r="M32" s="4">
-        <v>65242.23</v>
+        <v>42610</v>
       </c>
       <c r="N32" s="4">
-        <v>50299.17</v>
+        <v>43213.87</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2286,43 +2277,43 @@
         <v>45</v>
       </c>
       <c r="B35" s="4">
-        <v>667.5636111111112</v>
+        <v>0</v>
       </c>
       <c r="C35" s="4">
-        <v>760</v>
+        <v>2860.32</v>
       </c>
       <c r="D35" s="4">
-        <v>735.7</v>
+        <v>2962.19</v>
       </c>
       <c r="E35" s="4">
-        <v>667.5636111111112</v>
+        <v>0</v>
       </c>
       <c r="F35" s="4">
-        <v>4560</v>
+        <v>23138.99</v>
       </c>
       <c r="G35" s="4">
-        <v>735.7</v>
+        <v>2962.19</v>
       </c>
       <c r="H35" s="4">
-        <v>4504.83</v>
+        <v>21386.46</v>
       </c>
       <c r="I35" s="4">
-        <v>2087.287222222222</v>
+        <v>803.0555555555555</v>
       </c>
       <c r="J35" s="4">
-        <v>2685</v>
+        <v>16261.15</v>
       </c>
       <c r="K35" s="4">
-        <v>2770.24</v>
+        <v>15349.79</v>
       </c>
       <c r="L35" s="4">
-        <v>45304.32208333335</v>
+        <v>5843.437500000001</v>
       </c>
       <c r="M35" s="4">
-        <v>42610</v>
+        <v>141062.57</v>
       </c>
       <c r="N35" s="4">
-        <v>43213.87</v>
+        <v>148843.02</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2374,43 +2365,43 @@
         <v>47</v>
       </c>
       <c r="B37" s="4">
-        <v>0</v>
+        <v>135121.62</v>
       </c>
       <c r="C37" s="4">
-        <v>0</v>
+        <v>129074</v>
       </c>
       <c r="D37" s="4">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="E37" s="4">
-        <v>0</v>
+        <v>135121.62</v>
       </c>
       <c r="F37" s="4">
-        <v>0</v>
+        <v>1244139</v>
       </c>
       <c r="G37" s="4">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="H37" s="4">
-        <v>0</v>
+        <v>306838.21</v>
       </c>
       <c r="I37" s="4">
-        <v>0</v>
+        <v>982649.6800000001</v>
       </c>
       <c r="J37" s="4">
-        <v>0</v>
+        <v>1026256</v>
       </c>
       <c r="K37" s="4">
-        <v>0</v>
+        <v>429068.05</v>
       </c>
       <c r="L37" s="4">
-        <v>0</v>
+        <v>5218796.18</v>
       </c>
       <c r="M37" s="4">
-        <v>0</v>
+        <v>5577031</v>
       </c>
       <c r="N37" s="4">
-        <v>0</v>
+        <v>1536427.72</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2418,43 +2409,43 @@
         <v>48</v>
       </c>
       <c r="B38" s="4">
-        <v>3019.390375</v>
+        <v>262.8668194444444</v>
       </c>
       <c r="C38" s="4">
-        <v>2860.32</v>
+        <v>2318.6</v>
       </c>
       <c r="D38" s="4">
-        <v>2962.19</v>
+        <v>2297.33</v>
       </c>
       <c r="E38" s="4">
-        <v>3019.390375</v>
+        <v>262.8668194444444</v>
       </c>
       <c r="F38" s="4">
-        <v>23138.99</v>
+        <v>16087.97</v>
       </c>
       <c r="G38" s="4">
-        <v>2962.19</v>
+        <v>2297.33</v>
       </c>
       <c r="H38" s="4">
-        <v>21386.46</v>
+        <v>14744.23</v>
       </c>
       <c r="I38" s="4">
-        <v>17665.28118055555</v>
+        <v>762.7101527777778</v>
       </c>
       <c r="J38" s="4">
-        <v>16261.15</v>
+        <v>13221.53</v>
       </c>
       <c r="K38" s="4">
-        <v>15349.79</v>
+        <v>11696.88</v>
       </c>
       <c r="L38" s="4">
-        <v>191409.6784305555</v>
+        <v>3518.665486111111</v>
       </c>
       <c r="M38" s="4">
-        <v>141062.57</v>
+        <v>102041.61</v>
       </c>
       <c r="N38" s="4">
-        <v>148843.02</v>
+        <v>101419.92</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2462,43 +2453,43 @@
         <v>49</v>
       </c>
       <c r="B39" s="5">
-        <v>0</v>
+        <v>0.1945409028136611</v>
       </c>
       <c r="C39" s="5">
-        <v>0</v>
+        <v>1.796333885987883</v>
       </c>
       <c r="D39" s="5">
-        <v>0</v>
+        <v>5562.542372881356</v>
       </c>
       <c r="E39" s="5">
-        <v>0</v>
+        <v>0.1945409028136611</v>
       </c>
       <c r="F39" s="5">
-        <v>0</v>
+        <v>1.293100690517699</v>
       </c>
       <c r="G39" s="5">
-        <v>0</v>
+        <v>5562.542372881356</v>
       </c>
       <c r="H39" s="5">
-        <v>0</v>
+        <v>4.805213144738395</v>
       </c>
       <c r="I39" s="5">
-        <v>0</v>
+        <v>0.07761770733775417</v>
       </c>
       <c r="J39" s="5">
-        <v>0</v>
+        <v>1.288326694314089</v>
       </c>
       <c r="K39" s="5">
-        <v>0</v>
+        <v>2.726113025661081</v>
       </c>
       <c r="L39" s="5">
-        <v>0</v>
+        <v>0.06742293365653362</v>
       </c>
       <c r="M39" s="5">
-        <v>0</v>
+        <v>1.829676220196732</v>
       </c>
       <c r="N39" s="5">
-        <v>0</v>
+        <v>6.601021231249329</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2506,43 +2497,43 @@
         <v>50</v>
       </c>
       <c r="B40" s="4">
-        <v>135121.62</v>
+        <v>8266.98</v>
       </c>
       <c r="C40" s="4">
-        <v>129074</v>
+        <v>13937</v>
       </c>
       <c r="D40" s="4">
-        <v>217537.56</v>
+        <v>8859.299999999999</v>
       </c>
       <c r="E40" s="4">
-        <v>135121.62</v>
+        <v>8266.98</v>
       </c>
       <c r="F40" s="4">
-        <v>1244139</v>
+        <v>135771</v>
       </c>
       <c r="G40" s="4">
-        <v>217537.56</v>
+        <v>8859.299999999999</v>
       </c>
       <c r="H40" s="4">
-        <v>1349936.12</v>
+        <v>48937.49</v>
       </c>
       <c r="I40" s="4">
-        <v>982649.6800000001</v>
+        <v>73617.98</v>
       </c>
       <c r="J40" s="4">
-        <v>1026256</v>
+        <v>115095</v>
       </c>
       <c r="K40" s="4">
-        <v>1260470.39</v>
+        <v>127393.68</v>
       </c>
       <c r="L40" s="4">
-        <v>5218796.18</v>
+        <v>500394.68</v>
       </c>
       <c r="M40" s="4">
-        <v>5577031</v>
+        <v>759060</v>
       </c>
       <c r="N40" s="4">
-        <v>7457271.5</v>
+        <v>407099.16</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2550,43 +2541,43 @@
         <v>51</v>
       </c>
       <c r="B41" s="4">
-        <v>2634.665402777778</v>
+        <v>0</v>
       </c>
       <c r="C41" s="4">
-        <v>2318.6</v>
+        <v>4617.55</v>
       </c>
       <c r="D41" s="4">
-        <v>2297.33</v>
+        <v>4225.85</v>
       </c>
       <c r="E41" s="4">
-        <v>2634.665402777777</v>
+        <v>0</v>
       </c>
       <c r="F41" s="4">
-        <v>16087.97</v>
+        <v>47865.55</v>
       </c>
       <c r="G41" s="4">
-        <v>2297.33</v>
+        <v>4225.85</v>
       </c>
       <c r="H41" s="4">
-        <v>14744.23</v>
+        <v>32544.25</v>
       </c>
       <c r="I41" s="4">
-        <v>13899.26458333333</v>
+        <v>248</v>
       </c>
       <c r="J41" s="4">
-        <v>13221.53</v>
+        <v>27605.9</v>
       </c>
       <c r="K41" s="4">
-        <v>11696.88</v>
+        <v>96679.41</v>
       </c>
       <c r="L41" s="4">
-        <v>120065.4043472222</v>
+        <v>4784.32</v>
       </c>
       <c r="M41" s="4">
-        <v>102041.61</v>
+        <v>237955.21</v>
       </c>
       <c r="N41" s="4">
-        <v>101419.92</v>
+        <v>401994.5</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2594,43 +2585,43 @@
         <v>52</v>
       </c>
       <c r="B42" s="5">
-        <v>1.949847406194344</v>
+        <v>0</v>
       </c>
       <c r="C42" s="5">
-        <v>1.796333885987883</v>
+        <v>33.13159216474133</v>
       </c>
       <c r="D42" s="5">
-        <v>1.056061307297921</v>
+        <v>47.69959251859628</v>
       </c>
       <c r="E42" s="5">
-        <v>1.949847406194343</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5">
-        <v>1.293100690517699</v>
+        <v>35.25461991146857</v>
       </c>
       <c r="G42" s="5">
-        <v>1.056061307297921</v>
+        <v>47.69959251859628</v>
       </c>
       <c r="H42" s="5">
-        <v>1.092216867269245</v>
+        <v>66.50167387007384</v>
       </c>
       <c r="I42" s="5">
-        <v>1.4144679295406</v>
+        <v>0.3368742255628313</v>
       </c>
       <c r="J42" s="5">
-        <v>1.288326694314089</v>
+        <v>23.98531647769234</v>
       </c>
       <c r="K42" s="5">
-        <v>0.9279773720031614</v>
+        <v>75.89027179370279</v>
       </c>
       <c r="L42" s="5">
-        <v>2.300634096563284</v>
+        <v>0.9561092855743389</v>
       </c>
       <c r="M42" s="5">
-        <v>1.829676220196732</v>
+        <v>31.348669406898</v>
       </c>
       <c r="N42" s="5">
-        <v>1.360013779838913</v>
+        <v>98.74608928203143</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2638,43 +2629,43 @@
         <v>53</v>
       </c>
       <c r="B43" s="4">
-        <v>8266.98</v>
+        <v>38083.76</v>
       </c>
       <c r="C43" s="4">
-        <v>13937</v>
+        <v>28275</v>
       </c>
       <c r="D43" s="4">
-        <v>14702.3</v>
+        <v>18.71</v>
       </c>
       <c r="E43" s="4">
-        <v>8266.98</v>
+        <v>38083.76</v>
       </c>
       <c r="F43" s="4">
-        <v>135771</v>
+        <v>245076</v>
       </c>
       <c r="G43" s="4">
-        <v>14702.3</v>
+        <v>18.71</v>
       </c>
       <c r="H43" s="4">
-        <v>103791.42</v>
+        <v>126305.01</v>
       </c>
       <c r="I43" s="4">
-        <v>73617.98</v>
+        <v>259998.55</v>
       </c>
       <c r="J43" s="4">
-        <v>115095</v>
+        <v>234552</v>
       </c>
       <c r="K43" s="4">
-        <v>148654.68</v>
+        <v>243398.76</v>
       </c>
       <c r="L43" s="4">
-        <v>500394.68</v>
+        <v>1471396.02</v>
       </c>
       <c r="M43" s="4">
-        <v>759060</v>
+        <v>1445046</v>
       </c>
       <c r="N43" s="4">
-        <v>637601.89</v>
+        <v>1074266.93</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2682,43 +2673,43 @@
         <v>54</v>
       </c>
       <c r="B44" s="4">
-        <v>1121.908847222222</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4">
-        <v>4617.55</v>
+        <v>2162.95</v>
       </c>
       <c r="D44" s="4">
-        <v>4225.85</v>
+        <v>3012.71</v>
       </c>
       <c r="E44" s="4">
-        <v>1121.908847222222</v>
+        <v>0</v>
       </c>
       <c r="F44" s="4">
-        <v>47865.55</v>
+        <v>17334.32</v>
       </c>
       <c r="G44" s="4">
-        <v>4225.85</v>
+        <v>3012.71</v>
       </c>
       <c r="H44" s="4">
-        <v>32544.25</v>
+        <v>17650.8</v>
       </c>
       <c r="I44" s="4">
-        <v>13483.71518055555</v>
+        <v>302.9244166666667</v>
       </c>
       <c r="J44" s="4">
-        <v>27605.9</v>
+        <v>14302.66</v>
       </c>
       <c r="K44" s="4">
-        <v>96679.41</v>
+        <v>14728.12</v>
       </c>
       <c r="L44" s="4">
-        <v>238345.9120138889</v>
+        <v>2064.372333333334</v>
       </c>
       <c r="M44" s="4">
-        <v>237955.21</v>
+        <v>103249.3</v>
       </c>
       <c r="N44" s="4">
-        <v>401994.5</v>
+        <v>108756.65</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2726,43 +2717,43 @@
         <v>55</v>
       </c>
       <c r="B45" s="5">
-        <v>13.57096360729338</v>
+        <v>0</v>
       </c>
       <c r="C45" s="5">
-        <v>33.13159216474133</v>
+        <v>7.649690539345712</v>
       </c>
       <c r="D45" s="5">
-        <v>28.74278174163227</v>
+        <v>16102.13789417424</v>
       </c>
       <c r="E45" s="5">
-        <v>13.57096360729338</v>
+        <v>0</v>
       </c>
       <c r="F45" s="5">
-        <v>35.25461991146857</v>
+        <v>7.073038567628001</v>
       </c>
       <c r="G45" s="5">
-        <v>28.74278174163227</v>
+        <v>16102.13789417424</v>
       </c>
       <c r="H45" s="5">
-        <v>31.35543381138826</v>
+        <v>13.97474256959403</v>
       </c>
       <c r="I45" s="5">
-        <v>18.3157907627397</v>
+        <v>0.1165100407931762</v>
       </c>
       <c r="J45" s="5">
-        <v>23.98531647769234</v>
+        <v>6.097863160407926</v>
       </c>
       <c r="K45" s="5">
-        <v>65.03623700242738</v>
+        <v>6.051025075066118</v>
       </c>
       <c r="L45" s="5">
-        <v>47.63158393568231</v>
+        <v>0.1403002526358154</v>
       </c>
       <c r="M45" s="5">
-        <v>31.348669406898</v>
+        <v>7.145052821847885</v>
       </c>
       <c r="N45" s="5">
-        <v>63.04788400172402</v>
+        <v>10.12380135354255</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2770,43 +2761,43 @@
         <v>56</v>
       </c>
       <c r="B46" s="4">
-        <v>38083.76</v>
+        <v>0</v>
       </c>
       <c r="C46" s="4">
-        <v>28275</v>
+        <v>1361</v>
       </c>
       <c r="D46" s="4">
-        <v>43427.2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4">
-        <v>38083.76</v>
+        <v>0</v>
       </c>
       <c r="F46" s="4">
-        <v>245076</v>
+        <v>6983</v>
       </c>
       <c r="G46" s="4">
-        <v>43427.2</v>
+        <v>0</v>
       </c>
       <c r="H46" s="4">
-        <v>214421.76</v>
+        <v>0</v>
       </c>
       <c r="I46" s="4">
-        <v>259998.55</v>
+        <v>0</v>
       </c>
       <c r="J46" s="4">
-        <v>234552</v>
+        <v>5435</v>
       </c>
       <c r="K46" s="4">
-        <v>245738.76</v>
+        <v>0</v>
       </c>
       <c r="L46" s="4">
-        <v>1471396.02</v>
+        <v>0</v>
       </c>
       <c r="M46" s="4">
-        <v>1445046</v>
+        <v>35389</v>
       </c>
       <c r="N46" s="4">
-        <v>1484376.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2814,43 +2805,43 @@
         <v>57</v>
       </c>
       <c r="B47" s="4">
-        <v>2469.532527777777</v>
+        <v>0</v>
       </c>
       <c r="C47" s="4">
-        <v>2162.95</v>
+        <v>312</v>
       </c>
       <c r="D47" s="4">
-        <v>3012.71</v>
+        <v>294.21</v>
       </c>
       <c r="E47" s="4">
-        <v>2469.532527777778</v>
+        <v>0</v>
       </c>
       <c r="F47" s="4">
-        <v>17334.32</v>
+        <v>2218</v>
       </c>
       <c r="G47" s="4">
-        <v>3012.71</v>
+        <v>294.21</v>
       </c>
       <c r="H47" s="4">
-        <v>17650.8</v>
+        <v>2283.49</v>
       </c>
       <c r="I47" s="4">
-        <v>13132.78180555556</v>
+        <v>115.9381944444444</v>
       </c>
       <c r="J47" s="4">
-        <v>14302.66</v>
+        <v>1661</v>
       </c>
       <c r="K47" s="4">
-        <v>14728.12</v>
+        <v>1632.97</v>
       </c>
       <c r="L47" s="4">
-        <v>96240.83883333314</v>
+        <v>115.9381944444444</v>
       </c>
       <c r="M47" s="4">
-        <v>103249.3</v>
+        <v>20767.2</v>
       </c>
       <c r="N47" s="4">
-        <v>108756.65</v>
+        <v>20799.21</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2858,43 +2849,43 @@
         <v>58</v>
       </c>
       <c r="B48" s="5">
-        <v>6.484476658233791</v>
+        <v>0</v>
       </c>
       <c r="C48" s="5">
-        <v>7.649690539345712</v>
+        <v>22.92432035268185</v>
       </c>
       <c r="D48" s="5">
-        <v>6.937380259376612</v>
+        <v>0</v>
       </c>
       <c r="E48" s="5">
-        <v>6.484476658233793</v>
+        <v>0</v>
       </c>
       <c r="F48" s="5">
-        <v>7.073038567628001</v>
+        <v>31.76285264213089</v>
       </c>
       <c r="G48" s="5">
-        <v>6.937380259376612</v>
+        <v>0</v>
       </c>
       <c r="H48" s="5">
-        <v>8.231813786063503</v>
+        <v>0</v>
       </c>
       <c r="I48" s="5">
-        <v>5.051098094799205</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5">
-        <v>6.097863160407926</v>
+        <v>30.56117755289788</v>
       </c>
       <c r="K48" s="5">
-        <v>5.99340535453178</v>
+        <v>0</v>
       </c>
       <c r="L48" s="5">
-        <v>6.540784229750271</v>
+        <v>0</v>
       </c>
       <c r="M48" s="5">
-        <v>7.145052821847885</v>
+        <v>58.68264149877081</v>
       </c>
       <c r="N48" s="5">
-        <v>7.326754954178447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2902,43 +2893,43 @@
         <v>59</v>
       </c>
       <c r="B49" s="4">
-        <v>0</v>
+        <v>922.4</v>
       </c>
       <c r="C49" s="4">
-        <v>1361</v>
+        <v>846.11</v>
       </c>
       <c r="D49" s="4">
-        <v>0</v>
+        <v>698.59</v>
       </c>
       <c r="E49" s="4">
-        <v>0</v>
+        <v>922.4</v>
       </c>
       <c r="F49" s="4">
-        <v>6983</v>
+        <v>7486.36</v>
       </c>
       <c r="G49" s="4">
-        <v>0</v>
+        <v>698.59</v>
       </c>
       <c r="H49" s="4">
-        <v>0</v>
+        <v>6130.38</v>
       </c>
       <c r="I49" s="4">
-        <v>0</v>
+        <v>5785.69</v>
       </c>
       <c r="J49" s="4">
-        <v>5435</v>
+        <v>5889.2</v>
       </c>
       <c r="K49" s="4">
-        <v>0</v>
+        <v>4058.04</v>
       </c>
       <c r="L49" s="4">
-        <v>0</v>
+        <v>26069.68</v>
       </c>
       <c r="M49" s="4">
-        <v>35389</v>
+        <v>43943.49</v>
       </c>
       <c r="N49" s="4">
-        <v>0</v>
+        <v>51128.39</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2946,43 +2937,43 @@
         <v>60</v>
       </c>
       <c r="B50" s="4">
-        <v>162.6138194444445</v>
+        <v>0</v>
       </c>
       <c r="C50" s="4">
-        <v>312</v>
+        <v>182.16</v>
       </c>
       <c r="D50" s="4">
-        <v>294.21</v>
+        <v>173.31</v>
       </c>
       <c r="E50" s="4">
-        <v>162.6138194444445</v>
+        <v>0</v>
       </c>
       <c r="F50" s="4">
-        <v>2218</v>
+        <v>1275.12</v>
       </c>
       <c r="G50" s="4">
-        <v>294.21</v>
+        <v>173.31</v>
       </c>
       <c r="H50" s="4">
-        <v>2283.49</v>
+        <v>1138.72</v>
       </c>
       <c r="I50" s="4">
-        <v>1285.074902777778</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4">
-        <v>1661</v>
+        <v>910.8</v>
       </c>
       <c r="K50" s="4">
-        <v>1632.97</v>
+        <v>880.65</v>
       </c>
       <c r="L50" s="4">
-        <v>17194.73719444445</v>
+        <v>0</v>
       </c>
       <c r="M50" s="4">
-        <v>20767.2</v>
+        <v>8379.360000000001</v>
       </c>
       <c r="N50" s="4">
-        <v>20799.21</v>
+        <v>10834.82</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2993,40 +2984,40 @@
         <v>0</v>
       </c>
       <c r="C51" s="5">
-        <v>22.92432035268185</v>
+        <v>21.52911559962653</v>
       </c>
       <c r="D51" s="5">
-        <v>0</v>
+        <v>24.8085429221718</v>
       </c>
       <c r="E51" s="5">
         <v>0</v>
       </c>
       <c r="F51" s="5">
-        <v>31.76285264213089</v>
+        <v>17.03257657927217</v>
       </c>
       <c r="G51" s="5">
-        <v>0</v>
+        <v>24.8085429221718</v>
       </c>
       <c r="H51" s="5">
-        <v>0</v>
+        <v>18.5750312378678</v>
       </c>
       <c r="I51" s="5">
         <v>0</v>
       </c>
       <c r="J51" s="5">
-        <v>30.56117755289788</v>
+        <v>15.46559804387693</v>
       </c>
       <c r="K51" s="5">
-        <v>0</v>
+        <v>21.70136321968241</v>
       </c>
       <c r="L51" s="5">
         <v>0</v>
       </c>
       <c r="M51" s="5">
-        <v>58.68264149877081</v>
+        <v>19.06849000841763</v>
       </c>
       <c r="N51" s="5">
-        <v>0</v>
+        <v>21.19139679540076</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3034,43 +3025,43 @@
         <v>62</v>
       </c>
       <c r="B52" s="4">
-        <v>922.4</v>
+        <v>10816.47</v>
       </c>
       <c r="C52" s="4">
-        <v>846.11</v>
+        <v>14140.19</v>
       </c>
       <c r="D52" s="4">
-        <v>698.59</v>
+        <v>13442.54</v>
       </c>
       <c r="E52" s="4">
-        <v>922.4</v>
+        <v>10816.47</v>
       </c>
       <c r="F52" s="4">
-        <v>7486.36</v>
+        <v>118177.92</v>
       </c>
       <c r="G52" s="4">
-        <v>698.59</v>
+        <v>13442.54</v>
       </c>
       <c r="H52" s="4">
-        <v>6130.38</v>
+        <v>79095.03</v>
       </c>
       <c r="I52" s="4">
-        <v>5785.69</v>
+        <v>82622.67</v>
       </c>
       <c r="J52" s="4">
-        <v>5889.2</v>
+        <v>89482.86</v>
       </c>
       <c r="K52" s="4">
-        <v>4058.04</v>
+        <v>62894.6</v>
       </c>
       <c r="L52" s="4">
-        <v>26069.68</v>
+        <v>595129.63</v>
       </c>
       <c r="M52" s="4">
-        <v>43943.49</v>
+        <v>571489.15</v>
       </c>
       <c r="N52" s="4">
-        <v>65311.26</v>
+        <v>365835.91</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3078,43 +3069,43 @@
         <v>63</v>
       </c>
       <c r="B53" s="4">
-        <v>165.9145833333334</v>
+        <v>0</v>
       </c>
       <c r="C53" s="4">
-        <v>182.16</v>
+        <v>468.05</v>
       </c>
       <c r="D53" s="4">
-        <v>173.31</v>
+        <v>666.9400000000001</v>
       </c>
       <c r="E53" s="4">
-        <v>165.9145833333334</v>
+        <v>0</v>
       </c>
       <c r="F53" s="4">
-        <v>1275.12</v>
+        <v>3772.76</v>
       </c>
       <c r="G53" s="4">
-        <v>173.31</v>
+        <v>666.9400000000001</v>
       </c>
       <c r="H53" s="4">
-        <v>1138.72</v>
+        <v>4877.4</v>
       </c>
       <c r="I53" s="4">
-        <v>559.7344861111112</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4">
-        <v>910.8</v>
+        <v>2781.49</v>
       </c>
       <c r="K53" s="4">
-        <v>880.65</v>
+        <v>2969.46</v>
       </c>
       <c r="L53" s="4">
-        <v>4985.334694444444</v>
+        <v>0</v>
       </c>
       <c r="M53" s="4">
-        <v>8379.360000000001</v>
+        <v>33288.34</v>
       </c>
       <c r="N53" s="4">
-        <v>10834.82</v>
+        <v>40349.55</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -3122,43 +3113,43 @@
         <v>64</v>
       </c>
       <c r="B54" s="5">
-        <v>17.98727052616363</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5">
-        <v>21.52911559962653</v>
+        <v>3.310068676587797</v>
       </c>
       <c r="D54" s="5">
-        <v>24.8085429221718</v>
+        <v>4.961413542381128</v>
       </c>
       <c r="E54" s="5">
-        <v>17.98727052616363</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5">
-        <v>17.03257657927217</v>
+        <v>3.192440686043553</v>
       </c>
       <c r="G54" s="5">
-        <v>24.8085429221718</v>
+        <v>4.961413542381128</v>
       </c>
       <c r="H54" s="5">
-        <v>18.5750312378678</v>
+        <v>6.166506289965374</v>
       </c>
       <c r="I54" s="5">
-        <v>9.674463825595758</v>
+        <v>0</v>
       </c>
       <c r="J54" s="5">
-        <v>15.46559804387693</v>
+        <v>3.108405341536915</v>
       </c>
       <c r="K54" s="5">
-        <v>21.70136321968241</v>
+        <v>4.721327427155908</v>
       </c>
       <c r="L54" s="5">
-        <v>19.12311426317639</v>
+        <v>0</v>
       </c>
       <c r="M54" s="5">
-        <v>19.06849000841763</v>
+        <v>5.824841993938117</v>
       </c>
       <c r="N54" s="5">
-        <v>16.58951304874535</v>
+        <v>11.0294120661911</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3166,43 +3157,43 @@
         <v>65</v>
       </c>
       <c r="B55" s="4">
-        <v>10816.47</v>
+        <v>0</v>
       </c>
       <c r="C55" s="4">
-        <v>14140.19</v>
+        <v>0</v>
       </c>
       <c r="D55" s="4">
-        <v>14141.13</v>
+        <v>0</v>
       </c>
       <c r="E55" s="4">
-        <v>10816.47</v>
+        <v>0</v>
       </c>
       <c r="F55" s="4">
-        <v>118177.92</v>
+        <v>0</v>
       </c>
       <c r="G55" s="4">
-        <v>14141.13</v>
+        <v>0</v>
       </c>
       <c r="H55" s="4">
-        <v>103047.61</v>
+        <v>0</v>
       </c>
       <c r="I55" s="4">
-        <v>82622.67</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4">
-        <v>89482.86</v>
+        <v>0</v>
       </c>
       <c r="K55" s="4">
-        <v>65345.49</v>
+        <v>0</v>
       </c>
       <c r="L55" s="4">
-        <v>595129.63</v>
+        <v>0</v>
       </c>
       <c r="M55" s="4">
-        <v>571489.15</v>
+        <v>0</v>
       </c>
       <c r="N55" s="4">
-        <v>516509.03</v>
+        <v>1304.99</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3210,43 +3201,43 @@
         <v>66</v>
       </c>
       <c r="B56" s="4">
-        <v>500.9529722222222</v>
+        <v>0</v>
       </c>
       <c r="C56" s="4">
-        <v>468.05</v>
+        <v>0</v>
       </c>
       <c r="D56" s="4">
-        <v>666.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="E56" s="4">
-        <v>500.9529722222222</v>
+        <v>0</v>
       </c>
       <c r="F56" s="4">
-        <v>3772.76</v>
+        <v>0</v>
       </c>
       <c r="G56" s="4">
-        <v>666.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4">
-        <v>4877.4</v>
+        <v>0</v>
       </c>
       <c r="I56" s="4">
-        <v>3092.263930555555</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4">
-        <v>2781.49</v>
+        <v>0</v>
       </c>
       <c r="K56" s="4">
-        <v>2969.46</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4">
-        <v>38818.28444444444</v>
+        <v>0</v>
       </c>
       <c r="M56" s="4">
-        <v>33288.34</v>
+        <v>0</v>
       </c>
       <c r="N56" s="4">
-        <v>40349.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3254,43 +3245,43 @@
         <v>67</v>
       </c>
       <c r="B57" s="5">
-        <v>4.631390575873851</v>
+        <v>0</v>
       </c>
       <c r="C57" s="5">
-        <v>3.310068676587797</v>
+        <v>0</v>
       </c>
       <c r="D57" s="5">
-        <v>4.716313335638666</v>
+        <v>0</v>
       </c>
       <c r="E57" s="5">
-        <v>4.631390575873851</v>
+        <v>0</v>
       </c>
       <c r="F57" s="5">
-        <v>3.192440686043553</v>
+        <v>0</v>
       </c>
       <c r="G57" s="5">
-        <v>4.716313335638666</v>
+        <v>0</v>
       </c>
       <c r="H57" s="5">
-        <v>4.733151986737004</v>
+        <v>0</v>
       </c>
       <c r="I57" s="5">
-        <v>3.742633747560513</v>
+        <v>0</v>
       </c>
       <c r="J57" s="5">
-        <v>3.108405341536915</v>
+        <v>0</v>
       </c>
       <c r="K57" s="5">
-        <v>4.544246282337159</v>
+        <v>0</v>
       </c>
       <c r="L57" s="5">
-        <v>6.522660356273042</v>
+        <v>0</v>
       </c>
       <c r="M57" s="5">
-        <v>5.824841993938117</v>
+        <v>0</v>
       </c>
       <c r="N57" s="5">
-        <v>7.811973780981138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3298,43 +3289,43 @@
         <v>68</v>
       </c>
       <c r="B58" s="4">
-        <v>0</v>
+        <v>271.87</v>
       </c>
       <c r="C58" s="4">
-        <v>0</v>
+        <v>261.65</v>
       </c>
       <c r="D58" s="4">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="E58" s="4">
-        <v>0</v>
+        <v>271.87</v>
       </c>
       <c r="F58" s="4">
-        <v>0</v>
+        <v>1734.43</v>
       </c>
       <c r="G58" s="4">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="H58" s="4">
-        <v>0</v>
+        <v>75.08</v>
       </c>
       <c r="I58" s="4">
-        <v>0</v>
+        <v>1713.39</v>
       </c>
       <c r="J58" s="4">
-        <v>0</v>
+        <v>1404.5</v>
       </c>
       <c r="K58" s="4">
-        <v>0</v>
+        <v>61.26</v>
       </c>
       <c r="L58" s="4">
-        <v>0</v>
+        <v>4405.29</v>
       </c>
       <c r="M58" s="4">
-        <v>0</v>
+        <v>8653.530000000001</v>
       </c>
       <c r="N58" s="4">
-        <v>1304.99</v>
+        <v>335.5</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3345,40 +3336,40 @@
         <v>0</v>
       </c>
       <c r="C59" s="4">
-        <v>0</v>
+        <v>270.38</v>
       </c>
       <c r="D59" s="4">
-        <v>0</v>
+        <v>159.75</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
       </c>
       <c r="F59" s="4">
-        <v>0</v>
+        <v>1660.9</v>
       </c>
       <c r="G59" s="4">
-        <v>0</v>
+        <v>159.75</v>
       </c>
       <c r="H59" s="4">
-        <v>0</v>
+        <v>1321.25</v>
       </c>
       <c r="I59" s="4">
         <v>0</v>
       </c>
       <c r="J59" s="4">
-        <v>0</v>
+        <v>1602.96</v>
       </c>
       <c r="K59" s="4">
-        <v>0</v>
+        <v>1474.61</v>
       </c>
       <c r="L59" s="4">
         <v>0</v>
       </c>
       <c r="M59" s="4">
-        <v>0</v>
+        <v>12784.96</v>
       </c>
       <c r="N59" s="4">
-        <v>0</v>
+        <v>12332.01</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3389,40 +3380,40 @@
         <v>0</v>
       </c>
       <c r="C60" s="5">
-        <v>0</v>
+        <v>103.33651824957</v>
       </c>
       <c r="D60" s="5">
-        <v>0</v>
+        <v>2847.5935828877</v>
       </c>
       <c r="E60" s="5">
         <v>0</v>
       </c>
       <c r="F60" s="5">
-        <v>0</v>
+        <v>95.7605668721136</v>
       </c>
       <c r="G60" s="5">
-        <v>0</v>
+        <v>2847.5935828877</v>
       </c>
       <c r="H60" s="5">
-        <v>0</v>
+        <v>1759.789557805008</v>
       </c>
       <c r="I60" s="5">
         <v>0</v>
       </c>
       <c r="J60" s="5">
-        <v>0</v>
+        <v>114.1302954788181</v>
       </c>
       <c r="K60" s="5">
-        <v>0</v>
+        <v>2407.133529219719</v>
       </c>
       <c r="L60" s="5">
         <v>0</v>
       </c>
       <c r="M60" s="5">
-        <v>0</v>
+        <v>147.7427130893404</v>
       </c>
       <c r="N60" s="5">
-        <v>0</v>
+        <v>3675.71087928465</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3430,43 +3421,43 @@
         <v>71</v>
       </c>
       <c r="B61" s="4">
-        <v>271.87</v>
+        <v>0</v>
       </c>
       <c r="C61" s="4">
-        <v>261.65</v>
+        <v>0</v>
       </c>
       <c r="D61" s="4">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="E61" s="4">
-        <v>271.87</v>
+        <v>0</v>
       </c>
       <c r="F61" s="4">
-        <v>1734.43</v>
+        <v>0</v>
       </c>
       <c r="G61" s="4">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="H61" s="4">
-        <v>75.08</v>
+        <v>0</v>
       </c>
       <c r="I61" s="4">
-        <v>1713.39</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4">
-        <v>1404.5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4">
-        <v>61.26</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4">
-        <v>4405.29</v>
+        <v>0</v>
       </c>
       <c r="M61" s="4">
-        <v>8653.530000000001</v>
+        <v>0</v>
       </c>
       <c r="N61" s="4">
-        <v>348.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3474,43 +3465,43 @@
         <v>72</v>
       </c>
       <c r="B62" s="4">
-        <v>293.0149027777778</v>
+        <v>0</v>
       </c>
       <c r="C62" s="4">
-        <v>270.38</v>
+        <v>913.71</v>
       </c>
       <c r="D62" s="4">
-        <v>159.75</v>
+        <v>928.53</v>
       </c>
       <c r="E62" s="4">
-        <v>293.0149027777778</v>
+        <v>0</v>
       </c>
       <c r="F62" s="4">
-        <v>1660.9</v>
+        <v>6395.97</v>
       </c>
       <c r="G62" s="4">
-        <v>159.75</v>
+        <v>928.53</v>
       </c>
       <c r="H62" s="4">
-        <v>1321.25</v>
+        <v>6499.71</v>
       </c>
       <c r="I62" s="4">
-        <v>1019.481208333333</v>
+        <v>0</v>
       </c>
       <c r="J62" s="4">
-        <v>1602.96</v>
+        <v>4568.55</v>
       </c>
       <c r="K62" s="4">
-        <v>1474.61</v>
+        <v>4642.65</v>
       </c>
       <c r="L62" s="4">
-        <v>7175.175430555555</v>
+        <v>0</v>
       </c>
       <c r="M62" s="4">
-        <v>12784.96</v>
+        <v>60304.86</v>
       </c>
       <c r="N62" s="4">
-        <v>12332.01</v>
+        <v>61282.98</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3518,43 +3509,43 @@
         <v>73</v>
       </c>
       <c r="B63" s="5">
-        <v>107.7775785403972</v>
+        <v>0</v>
       </c>
       <c r="C63" s="5">
-        <v>103.33651824957</v>
+        <v>0</v>
       </c>
       <c r="D63" s="5">
-        <v>2847.5935828877</v>
+        <v>0</v>
       </c>
       <c r="E63" s="5">
-        <v>107.7775785403972</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5">
-        <v>95.7605668721136</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>2847.5935828877</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5">
-        <v>1759.789557805008</v>
+        <v>0</v>
       </c>
       <c r="I63" s="5">
-        <v>59.50082633453757</v>
+        <v>0</v>
       </c>
       <c r="J63" s="5">
-        <v>114.1302954788181</v>
+        <v>0</v>
       </c>
       <c r="K63" s="5">
-        <v>2407.133529219719</v>
+        <v>0</v>
       </c>
       <c r="L63" s="5">
-        <v>162.876347086243</v>
+        <v>0</v>
       </c>
       <c r="M63" s="5">
-        <v>147.7427130893404</v>
+        <v>0</v>
       </c>
       <c r="N63" s="5">
-        <v>3538.393779410078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3562,43 +3553,43 @@
         <v>74</v>
       </c>
       <c r="B64" s="4">
-        <v>0</v>
+        <v>8984.24</v>
       </c>
       <c r="C64" s="4">
-        <v>0</v>
+        <v>9158.4</v>
       </c>
       <c r="D64" s="4">
-        <v>0</v>
+        <v>8642.780000000001</v>
       </c>
       <c r="E64" s="4">
-        <v>0</v>
+        <v>8984.24</v>
       </c>
       <c r="F64" s="4">
-        <v>0</v>
+        <v>74889</v>
       </c>
       <c r="G64" s="4">
-        <v>0</v>
+        <v>8642.780000000001</v>
       </c>
       <c r="H64" s="4">
-        <v>0</v>
+        <v>39834.25</v>
       </c>
       <c r="I64" s="4">
-        <v>0</v>
+        <v>54356.29</v>
       </c>
       <c r="J64" s="4">
-        <v>0</v>
+        <v>57430.8</v>
       </c>
       <c r="K64" s="4">
-        <v>0</v>
+        <v>49104.47</v>
       </c>
       <c r="L64" s="4">
-        <v>0</v>
+        <v>523016.57</v>
       </c>
       <c r="M64" s="4">
-        <v>0</v>
+        <v>357082.2</v>
       </c>
       <c r="N64" s="4">
-        <v>0</v>
+        <v>424356.83</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3606,43 +3597,43 @@
         <v>75</v>
       </c>
       <c r="B65" s="4">
-        <v>940.28</v>
+        <v>150.2736666666667</v>
       </c>
       <c r="C65" s="4">
-        <v>913.71</v>
+        <v>1168.72</v>
       </c>
       <c r="D65" s="4">
-        <v>928.53</v>
+        <v>1208.09</v>
       </c>
       <c r="E65" s="4">
-        <v>940.28</v>
+        <v>150.2736666666667</v>
       </c>
       <c r="F65" s="4">
-        <v>6395.97</v>
+        <v>7757.12</v>
       </c>
       <c r="G65" s="4">
-        <v>928.53</v>
+        <v>1208.09</v>
       </c>
       <c r="H65" s="4">
-        <v>6499.71</v>
+        <v>8688.129999999999</v>
       </c>
       <c r="I65" s="4">
-        <v>4993.866</v>
+        <v>301.303</v>
       </c>
       <c r="J65" s="4">
-        <v>4568.55</v>
+        <v>6003.77</v>
       </c>
       <c r="K65" s="4">
-        <v>4642.65</v>
+        <v>8143.07</v>
       </c>
       <c r="L65" s="4">
-        <v>66443.61926388889</v>
+        <v>3617.153333333333</v>
       </c>
       <c r="M65" s="4">
-        <v>60304.86</v>
+        <v>65598.88</v>
       </c>
       <c r="N65" s="4">
-        <v>61282.98</v>
+        <v>70798.27</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3650,43 +3641,43 @@
         <v>76</v>
       </c>
       <c r="B66" s="5">
-        <v>0</v>
+        <v>1.672636379556497</v>
       </c>
       <c r="C66" s="5">
-        <v>0</v>
+        <v>12.76118099231307</v>
       </c>
       <c r="D66" s="5">
-        <v>0</v>
+        <v>13.97802558898873</v>
       </c>
       <c r="E66" s="5">
-        <v>0</v>
+        <v>1.672636379556497</v>
       </c>
       <c r="F66" s="5">
-        <v>0</v>
+        <v>10.35815673863985</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>13.97802558898873</v>
       </c>
       <c r="H66" s="5">
-        <v>0</v>
+        <v>21.81070310097466</v>
       </c>
       <c r="I66" s="5">
-        <v>0</v>
+        <v>0.5543111937919236</v>
       </c>
       <c r="J66" s="5">
-        <v>0</v>
+        <v>10.45392019613169</v>
       </c>
       <c r="K66" s="5">
-        <v>0</v>
+        <v>16.58315424237345</v>
       </c>
       <c r="L66" s="5">
-        <v>0</v>
+        <v>0.6915944046157722</v>
       </c>
       <c r="M66" s="5">
-        <v>0</v>
+        <v>18.37080649777558</v>
       </c>
       <c r="N66" s="5">
-        <v>0</v>
+        <v>16.68366454712182</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3694,43 +3685,43 @@
         <v>77</v>
       </c>
       <c r="B67" s="4">
-        <v>8984.24</v>
+        <v>21795.7</v>
       </c>
       <c r="C67" s="4">
-        <v>9158.4</v>
+        <v>17493.21</v>
       </c>
       <c r="D67" s="4">
-        <v>8642.780000000001</v>
+        <v>17424.16</v>
       </c>
       <c r="E67" s="4">
-        <v>8984.24</v>
+        <v>21795.7</v>
       </c>
       <c r="F67" s="4">
-        <v>74889</v>
+        <v>143043.4</v>
       </c>
       <c r="G67" s="4">
-        <v>8642.780000000001</v>
+        <v>17424.16</v>
       </c>
       <c r="H67" s="4">
-        <v>39834.25</v>
+        <v>113199.95</v>
       </c>
       <c r="I67" s="4">
-        <v>54356.29</v>
+        <v>128531.71</v>
       </c>
       <c r="J67" s="4">
-        <v>57430.8</v>
+        <v>109696.99</v>
       </c>
       <c r="K67" s="4">
-        <v>49104.47</v>
+        <v>99210.27</v>
       </c>
       <c r="L67" s="4">
-        <v>523016.57</v>
+        <v>860753.49</v>
       </c>
       <c r="M67" s="4">
-        <v>357082.2</v>
+        <v>682052.91</v>
       </c>
       <c r="N67" s="4">
-        <v>467299.93</v>
+        <v>547504.49</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3738,43 +3729,43 @@
         <v>78</v>
       </c>
       <c r="B68" s="4">
-        <v>1228.607888888889</v>
+        <v>214.7918333333333</v>
       </c>
       <c r="C68" s="4">
-        <v>1168.72</v>
+        <v>2597.04</v>
       </c>
       <c r="D68" s="4">
-        <v>1208.09</v>
+        <v>2527.64</v>
       </c>
       <c r="E68" s="4">
-        <v>1228.607888888889</v>
+        <v>214.7918333333333</v>
       </c>
       <c r="F68" s="4">
-        <v>7757.12</v>
+        <v>17820.02</v>
       </c>
       <c r="G68" s="4">
-        <v>1208.09</v>
+        <v>2527.64</v>
       </c>
       <c r="H68" s="4">
-        <v>8688.129999999999</v>
+        <v>17146.63</v>
       </c>
       <c r="I68" s="4">
-        <v>7312.869847222223</v>
+        <v>1029.638319444445</v>
       </c>
       <c r="J68" s="4">
-        <v>6003.77</v>
+        <v>12805.57</v>
       </c>
       <c r="K68" s="4">
-        <v>8143.07</v>
+        <v>13896.99</v>
       </c>
       <c r="L68" s="4">
-        <v>97507.0747222224</v>
+        <v>14394.35320833333</v>
       </c>
       <c r="M68" s="4">
-        <v>65598.88</v>
+        <v>98705.85000000001</v>
       </c>
       <c r="N68" s="4">
-        <v>70798.27</v>
+        <v>100657</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3782,43 +3773,43 @@
         <v>79</v>
       </c>
       <c r="B69" s="5">
-        <v>13.67514546460122</v>
+        <v>0.9854780224233831</v>
       </c>
       <c r="C69" s="5">
-        <v>12.76118099231307</v>
+        <v>14.84598881508883</v>
       </c>
       <c r="D69" s="5">
-        <v>13.97802558898873</v>
+        <v>14.50652427434092</v>
       </c>
       <c r="E69" s="5">
-        <v>13.67514546460122</v>
+        <v>0.9854780224233831</v>
       </c>
       <c r="F69" s="5">
-        <v>10.35815673863985</v>
+        <v>12.45777155744341</v>
       </c>
       <c r="G69" s="5">
-        <v>13.97802558898873</v>
+        <v>14.50652427434092</v>
       </c>
       <c r="H69" s="5">
-        <v>21.81070310097466</v>
+        <v>15.14720633710527</v>
       </c>
       <c r="I69" s="5">
-        <v>13.45358531132685</v>
+        <v>0.801077274584182</v>
       </c>
       <c r="J69" s="5">
-        <v>10.45392019613169</v>
+        <v>11.67358375102179</v>
       </c>
       <c r="K69" s="5">
-        <v>16.58315424237345</v>
+        <v>14.00761231674906</v>
       </c>
       <c r="L69" s="5">
-        <v>18.64320947273666</v>
+        <v>1.672296816168975</v>
       </c>
       <c r="M69" s="5">
-        <v>18.37080649777558</v>
+        <v>14.47187579626337</v>
       </c>
       <c r="N69" s="5">
-        <v>15.15049873857246</v>
+        <v>18.38468941140556</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3826,43 +3817,43 @@
         <v>80</v>
       </c>
       <c r="B70" s="4">
-        <v>21774.15</v>
+        <v>419.05</v>
       </c>
       <c r="C70" s="4">
-        <v>17493.21</v>
+        <v>1092.42</v>
       </c>
       <c r="D70" s="4">
-        <v>17424.16</v>
+        <v>672.6</v>
       </c>
       <c r="E70" s="4">
-        <v>21774.15</v>
+        <v>419.05</v>
       </c>
       <c r="F70" s="4">
-        <v>143043.4</v>
+        <v>7646.94</v>
       </c>
       <c r="G70" s="4">
-        <v>17424.16</v>
+        <v>672.6</v>
       </c>
       <c r="H70" s="4">
-        <v>113199.95</v>
+        <v>5211.42</v>
       </c>
       <c r="I70" s="4">
-        <v>128510.16</v>
+        <v>4199.51</v>
       </c>
       <c r="J70" s="4">
-        <v>109696.99</v>
+        <v>5462.1</v>
       </c>
       <c r="K70" s="4">
-        <v>99210.27</v>
+        <v>5790.43</v>
       </c>
       <c r="L70" s="4">
-        <v>860731.9399999999</v>
+        <v>57388.35</v>
       </c>
       <c r="M70" s="4">
-        <v>682052.91</v>
+        <v>62194.86</v>
       </c>
       <c r="N70" s="4">
-        <v>694567.2</v>
+        <v>53732.94</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3870,43 +3861,43 @@
         <v>81</v>
       </c>
       <c r="B71" s="4">
-        <v>3067.137916666667</v>
+        <v>0</v>
       </c>
       <c r="C71" s="4">
-        <v>2597.04</v>
+        <v>301.3</v>
       </c>
       <c r="D71" s="4">
-        <v>2527.64</v>
+        <v>329.53</v>
       </c>
       <c r="E71" s="4">
-        <v>3067.137916666667</v>
+        <v>0</v>
       </c>
       <c r="F71" s="4">
-        <v>17820.02</v>
+        <v>2772.82</v>
       </c>
       <c r="G71" s="4">
-        <v>2527.64</v>
+        <v>329.53</v>
       </c>
       <c r="H71" s="4">
-        <v>17146.63</v>
+        <v>2599.25</v>
       </c>
       <c r="I71" s="4">
-        <v>18292.11505555557</v>
+        <v>220.51825</v>
       </c>
       <c r="J71" s="4">
-        <v>12805.57</v>
+        <v>2189.47</v>
       </c>
       <c r="K71" s="4">
-        <v>13896.99</v>
+        <v>2282.68</v>
       </c>
       <c r="L71" s="4">
-        <v>144048.1436388893</v>
+        <v>719.6010000000001</v>
       </c>
       <c r="M71" s="4">
-        <v>98705.85000000001</v>
+        <v>25370.08</v>
       </c>
       <c r="N71" s="4">
-        <v>100657</v>
+        <v>25276.86</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3914,43 +3905,43 @@
         <v>82</v>
       </c>
       <c r="B72" s="5">
-        <v>14.0861430488293</v>
+        <v>0</v>
       </c>
       <c r="C72" s="5">
-        <v>14.84598881508883</v>
+        <v>27.58096702733381</v>
       </c>
       <c r="D72" s="5">
-        <v>14.50652427434092</v>
+        <v>48.99345822182575</v>
       </c>
       <c r="E72" s="5">
-        <v>14.08614304882931</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5">
-        <v>12.45777155744341</v>
+        <v>36.26051727880695</v>
       </c>
       <c r="G72" s="5">
-        <v>14.50652427434092</v>
+        <v>48.99345822182575</v>
       </c>
       <c r="H72" s="5">
-        <v>15.14720633710527</v>
+        <v>49.87604146278749</v>
       </c>
       <c r="I72" s="5">
-        <v>14.23398356640095</v>
+        <v>5.251047145976554</v>
       </c>
       <c r="J72" s="5">
-        <v>11.67358375102179</v>
+        <v>40.08476593251679</v>
       </c>
       <c r="K72" s="5">
-        <v>14.00761231674906</v>
+        <v>39.42159735978157</v>
       </c>
       <c r="L72" s="5">
-        <v>16.73554064217593</v>
+        <v>1.253914775385597</v>
       </c>
       <c r="M72" s="5">
-        <v>14.47187579626337</v>
+        <v>40.79128082288472</v>
       </c>
       <c r="N72" s="5">
-        <v>14.49204626996495</v>
+        <v>47.0416470790543</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3958,43 +3949,43 @@
         <v>83</v>
       </c>
       <c r="B73" s="4">
-        <v>419.05</v>
+        <v>1859.59</v>
       </c>
       <c r="C73" s="4">
-        <v>1092.42</v>
+        <v>3199.2</v>
       </c>
       <c r="D73" s="4">
-        <v>672.6</v>
+        <v>1383.35</v>
       </c>
       <c r="E73" s="4">
-        <v>419.05</v>
+        <v>1859.59</v>
       </c>
       <c r="F73" s="4">
-        <v>7646.94</v>
+        <v>26160.13</v>
       </c>
       <c r="G73" s="4">
-        <v>672.6</v>
+        <v>1383.35</v>
       </c>
       <c r="H73" s="4">
-        <v>5211.42</v>
+        <v>9630.799999999999</v>
       </c>
       <c r="I73" s="4">
-        <v>4199.51</v>
+        <v>19098.93</v>
       </c>
       <c r="J73" s="4">
-        <v>5462.1</v>
+        <v>20061.66</v>
       </c>
       <c r="K73" s="4">
-        <v>5790.43</v>
+        <v>10597.52</v>
       </c>
       <c r="L73" s="4">
-        <v>57388.35</v>
+        <v>83017.14</v>
       </c>
       <c r="M73" s="4">
-        <v>62194.86</v>
+        <v>70549.03999999999</v>
       </c>
       <c r="N73" s="4">
-        <v>66908.99000000001</v>
+        <v>32074.31</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -4002,43 +3993,43 @@
         <v>84</v>
       </c>
       <c r="B74" s="4">
-        <v>286.2029027777778</v>
+        <v>0</v>
       </c>
       <c r="C74" s="4">
-        <v>301.3</v>
+        <v>557.02</v>
       </c>
       <c r="D74" s="4">
-        <v>329.53</v>
+        <v>216.39</v>
       </c>
       <c r="E74" s="4">
-        <v>286.2029027777778</v>
+        <v>0</v>
       </c>
       <c r="F74" s="4">
-        <v>2772.82</v>
+        <v>4768.08</v>
       </c>
       <c r="G74" s="4">
-        <v>329.53</v>
+        <v>216.39</v>
       </c>
       <c r="H74" s="4">
-        <v>2599.25</v>
+        <v>1284.62</v>
       </c>
       <c r="I74" s="4">
-        <v>1775.092375</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4">
-        <v>2189.47</v>
+        <v>3671.34</v>
       </c>
       <c r="K74" s="4">
-        <v>2282.68</v>
+        <v>1149.8</v>
       </c>
       <c r="L74" s="4">
-        <v>25597.64534722222</v>
+        <v>75.61266666666666</v>
       </c>
       <c r="M74" s="4">
-        <v>25370.08</v>
+        <v>15072.95</v>
       </c>
       <c r="N74" s="4">
-        <v>25276.86</v>
+        <v>5615.58</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -4046,43 +4037,43 @@
         <v>85</v>
       </c>
       <c r="B75" s="5">
-        <v>68.29803192406104</v>
+        <v>0</v>
       </c>
       <c r="C75" s="5">
-        <v>27.58096702733381</v>
+        <v>17.41122780695174</v>
       </c>
       <c r="D75" s="5">
-        <v>48.99345822182575</v>
+        <v>15.64246213901037</v>
       </c>
       <c r="E75" s="5">
-        <v>68.29803192406104</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5">
-        <v>36.26051727880695</v>
+        <v>18.22651492939828</v>
       </c>
       <c r="G75" s="5">
-        <v>48.99345822182575</v>
+        <v>15.64246213901037</v>
       </c>
       <c r="H75" s="5">
-        <v>49.87604146278749</v>
+        <v>13.33866345474934</v>
       </c>
       <c r="I75" s="5">
-        <v>42.26903555414798</v>
+        <v>0</v>
       </c>
       <c r="J75" s="5">
-        <v>40.08476593251679</v>
+        <v>18.30028023603231</v>
       </c>
       <c r="K75" s="5">
-        <v>39.42159735978157</v>
+        <v>10.84970823362447</v>
       </c>
       <c r="L75" s="5">
-        <v>44.60425390732129</v>
+        <v>0.09108078966182966</v>
       </c>
       <c r="M75" s="5">
-        <v>40.79128082288472</v>
+        <v>21.36520922184058</v>
       </c>
       <c r="N75" s="5">
-        <v>37.77797273580127</v>
+        <v>17.50803057026012</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4090,43 +4081,43 @@
         <v>86</v>
       </c>
       <c r="B76" s="4">
-        <v>1859.59</v>
+        <v>0</v>
       </c>
       <c r="C76" s="4">
-        <v>3199.2</v>
+        <v>0</v>
       </c>
       <c r="D76" s="4">
-        <v>1383.35</v>
+        <v>0</v>
       </c>
       <c r="E76" s="4">
-        <v>1859.59</v>
+        <v>0</v>
       </c>
       <c r="F76" s="4">
-        <v>26160.13</v>
+        <v>0</v>
       </c>
       <c r="G76" s="4">
-        <v>1383.35</v>
+        <v>0</v>
       </c>
       <c r="H76" s="4">
-        <v>9630.799999999999</v>
+        <v>0</v>
       </c>
       <c r="I76" s="4">
-        <v>19098.93</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4">
-        <v>20061.66</v>
+        <v>0</v>
       </c>
       <c r="K76" s="4">
-        <v>10597.52</v>
+        <v>0</v>
       </c>
       <c r="L76" s="4">
-        <v>83017.14</v>
+        <v>0</v>
       </c>
       <c r="M76" s="4">
-        <v>70549.03999999999</v>
+        <v>0</v>
       </c>
       <c r="N76" s="4">
-        <v>36542.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -4134,43 +4125,43 @@
         <v>87</v>
       </c>
       <c r="B77" s="4">
-        <v>769.2560972222223</v>
+        <v>0</v>
       </c>
       <c r="C77" s="4">
-        <v>557.02</v>
+        <v>0</v>
       </c>
       <c r="D77" s="4">
-        <v>216.39</v>
+        <v>0</v>
       </c>
       <c r="E77" s="4">
-        <v>769.2560972222223</v>
+        <v>0</v>
       </c>
       <c r="F77" s="4">
-        <v>4768.08</v>
+        <v>0</v>
       </c>
       <c r="G77" s="4">
-        <v>216.39</v>
+        <v>0</v>
       </c>
       <c r="H77" s="4">
-        <v>1284.62</v>
+        <v>30.88</v>
       </c>
       <c r="I77" s="4">
-        <v>4700.658444444445</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4">
-        <v>3671.34</v>
+        <v>0</v>
       </c>
       <c r="K77" s="4">
-        <v>1149.8</v>
+        <v>0</v>
       </c>
       <c r="L77" s="4">
-        <v>24811.29855555557</v>
+        <v>0</v>
       </c>
       <c r="M77" s="4">
-        <v>15072.95</v>
+        <v>0</v>
       </c>
       <c r="N77" s="4">
-        <v>5615.58</v>
+        <v>216.21</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4178,43 +4169,43 @@
         <v>88</v>
       </c>
       <c r="B78" s="5">
-        <v>41.36697321572079</v>
+        <v>0</v>
       </c>
       <c r="C78" s="5">
-        <v>17.41122780695174</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5">
-        <v>15.64246213901037</v>
+        <v>0</v>
       </c>
       <c r="E78" s="5">
-        <v>41.36697321572079</v>
+        <v>0</v>
       </c>
       <c r="F78" s="5">
-        <v>18.22651492939828</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5">
-        <v>15.64246213901037</v>
+        <v>0</v>
       </c>
       <c r="H78" s="5">
-        <v>13.33866345474934</v>
+        <v>0</v>
       </c>
       <c r="I78" s="5">
-        <v>24.6121559922176</v>
+        <v>0</v>
       </c>
       <c r="J78" s="5">
-        <v>18.30028023603231</v>
+        <v>0</v>
       </c>
       <c r="K78" s="5">
-        <v>10.84970823362447</v>
+        <v>0</v>
       </c>
       <c r="L78" s="5">
-        <v>29.88695895276032</v>
+        <v>0</v>
       </c>
       <c r="M78" s="5">
-        <v>21.36520922184058</v>
+        <v>0</v>
       </c>
       <c r="N78" s="5">
-        <v>15.36706806648068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -4258,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="4">
-        <v>0</v>
+        <v>14447.95</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -4272,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -4281,10 +4272,10 @@
         <v>0</v>
       </c>
       <c r="G80" s="4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H80" s="4">
-        <v>30.88</v>
+        <v>175.5</v>
       </c>
       <c r="I80" s="4">
         <v>0</v>
@@ -4293,16 +4284,16 @@
         <v>0</v>
       </c>
       <c r="K80" s="4">
-        <v>0</v>
+        <v>198.9</v>
       </c>
       <c r="L80" s="4">
-        <v>237.4439027777778</v>
+        <v>0</v>
       </c>
       <c r="M80" s="4">
         <v>0</v>
       </c>
       <c r="N80" s="4">
-        <v>216.21</v>
+        <v>4704.46</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4346,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="5">
-        <v>0</v>
+        <v>32.56143605148135</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4357,40 +4348,40 @@
         <v>0</v>
       </c>
       <c r="C82" s="4">
-        <v>0</v>
+        <v>2838.68</v>
       </c>
       <c r="D82" s="4">
-        <v>0</v>
+        <v>2558.76</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
       </c>
       <c r="F82" s="4">
-        <v>0</v>
+        <v>22467.97</v>
       </c>
       <c r="G82" s="4">
-        <v>0</v>
+        <v>2558.76</v>
       </c>
       <c r="H82" s="4">
-        <v>0</v>
+        <v>22126.12</v>
       </c>
       <c r="I82" s="4">
         <v>0</v>
       </c>
       <c r="J82" s="4">
-        <v>0</v>
+        <v>20946.36</v>
       </c>
       <c r="K82" s="4">
-        <v>0</v>
+        <v>23807.43</v>
       </c>
       <c r="L82" s="4">
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <v>0</v>
+        <v>154576.78</v>
       </c>
       <c r="N82" s="4">
-        <v>14447.95</v>
+        <v>147632.81</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4398,43 +4389,43 @@
         <v>93</v>
       </c>
       <c r="B83" s="4">
-        <v>0</v>
+        <v>131.1419166666666</v>
       </c>
       <c r="C83" s="4">
-        <v>0</v>
+        <v>430.44</v>
       </c>
       <c r="D83" s="4">
-        <v>45</v>
+        <v>414.92</v>
       </c>
       <c r="E83" s="4">
-        <v>0</v>
+        <v>131.1419166666666</v>
       </c>
       <c r="F83" s="4">
-        <v>0</v>
+        <v>4085.08</v>
       </c>
       <c r="G83" s="4">
-        <v>45</v>
+        <v>414.92</v>
       </c>
       <c r="H83" s="4">
-        <v>175.5</v>
+        <v>4273.65</v>
       </c>
       <c r="I83" s="4">
-        <v>0</v>
+        <v>758.5172916666666</v>
       </c>
       <c r="J83" s="4">
-        <v>0</v>
+        <v>2795.4</v>
       </c>
       <c r="K83" s="4">
-        <v>198.9</v>
+        <v>2815.05</v>
       </c>
       <c r="L83" s="4">
-        <v>0</v>
+        <v>8189.641666666666</v>
       </c>
       <c r="M83" s="4">
-        <v>0</v>
+        <v>36616.64</v>
       </c>
       <c r="N83" s="4">
-        <v>4704.46</v>
+        <v>36445.53</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4445,40 +4436,40 @@
         <v>0</v>
       </c>
       <c r="C84" s="5">
-        <v>0</v>
+        <v>15.16338579903335</v>
       </c>
       <c r="D84" s="5">
-        <v>0</v>
+        <v>16.21566696368554</v>
       </c>
       <c r="E84" s="5">
         <v>0</v>
       </c>
       <c r="F84" s="5">
-        <v>0</v>
+        <v>18.1817939048343</v>
       </c>
       <c r="G84" s="5">
-        <v>0</v>
+        <v>16.21566696368554</v>
       </c>
       <c r="H84" s="5">
-        <v>0</v>
+        <v>19.31495445202322</v>
       </c>
       <c r="I84" s="5">
         <v>0</v>
       </c>
       <c r="J84" s="5">
-        <v>0</v>
+        <v>13.34551683442851</v>
       </c>
       <c r="K84" s="5">
-        <v>0</v>
+        <v>11.82424982452957</v>
       </c>
       <c r="L84" s="5">
         <v>0</v>
       </c>
       <c r="M84" s="5">
-        <v>0</v>
+        <v>23.68831851717962</v>
       </c>
       <c r="N84" s="5">
-        <v>32.56143605148135</v>
+        <v>24.68660591097602</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4489,40 +4480,40 @@
         <v>0</v>
       </c>
       <c r="C85" s="4">
-        <v>2838.68</v>
+        <v>0</v>
       </c>
       <c r="D85" s="4">
-        <v>2558.76</v>
+        <v>0</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
       </c>
       <c r="F85" s="4">
-        <v>22467.97</v>
+        <v>0</v>
       </c>
       <c r="G85" s="4">
-        <v>2558.76</v>
+        <v>0</v>
       </c>
       <c r="H85" s="4">
-        <v>22126.12</v>
+        <v>0</v>
       </c>
       <c r="I85" s="4">
         <v>0</v>
       </c>
       <c r="J85" s="4">
-        <v>20946.36</v>
+        <v>0</v>
       </c>
       <c r="K85" s="4">
-        <v>23807.43</v>
+        <v>0</v>
       </c>
       <c r="L85" s="4">
         <v>0</v>
       </c>
       <c r="M85" s="4">
-        <v>154576.78</v>
+        <v>0</v>
       </c>
       <c r="N85" s="4">
-        <v>156291.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4530,43 +4521,43 @@
         <v>96</v>
       </c>
       <c r="B86" s="4">
-        <v>452.58125</v>
+        <v>0</v>
       </c>
       <c r="C86" s="4">
-        <v>430.44</v>
+        <v>418.69</v>
       </c>
       <c r="D86" s="4">
-        <v>414.92</v>
+        <v>316.01</v>
       </c>
       <c r="E86" s="4">
-        <v>452.58125</v>
+        <v>0</v>
       </c>
       <c r="F86" s="4">
-        <v>4085.08</v>
+        <v>2659.14</v>
       </c>
       <c r="G86" s="4">
-        <v>414.92</v>
+        <v>316.01</v>
       </c>
       <c r="H86" s="4">
-        <v>4273.65</v>
+        <v>3600.74</v>
       </c>
       <c r="I86" s="4">
-        <v>3361.681055555556</v>
+        <v>578.256625</v>
       </c>
       <c r="J86" s="4">
-        <v>2795.4</v>
+        <v>1958.13</v>
       </c>
       <c r="K86" s="4">
-        <v>2815.05</v>
+        <v>2343.32</v>
       </c>
       <c r="L86" s="4">
-        <v>33421.17543055555</v>
+        <v>3601.116888888888</v>
       </c>
       <c r="M86" s="4">
-        <v>36616.64</v>
+        <v>20176.61</v>
       </c>
       <c r="N86" s="4">
-        <v>36445.53</v>
+        <v>23179.03</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4577,40 +4568,40 @@
         <v>0</v>
       </c>
       <c r="C87" s="5">
-        <v>15.16338579903335</v>
+        <v>0</v>
       </c>
       <c r="D87" s="5">
-        <v>16.21566696368554</v>
+        <v>0</v>
       </c>
       <c r="E87" s="5">
         <v>0</v>
       </c>
       <c r="F87" s="5">
-        <v>18.1817939048343</v>
+        <v>0</v>
       </c>
       <c r="G87" s="5">
-        <v>16.21566696368554</v>
+        <v>0</v>
       </c>
       <c r="H87" s="5">
-        <v>19.31495445202322</v>
+        <v>0</v>
       </c>
       <c r="I87" s="5">
         <v>0</v>
       </c>
       <c r="J87" s="5">
-        <v>13.34551683442851</v>
+        <v>0</v>
       </c>
       <c r="K87" s="5">
-        <v>11.82424982452957</v>
+        <v>0</v>
       </c>
       <c r="L87" s="5">
         <v>0</v>
       </c>
       <c r="M87" s="5">
-        <v>23.68831851717962</v>
+        <v>0</v>
       </c>
       <c r="N87" s="5">
-        <v>23.31892330780307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4662,43 +4653,43 @@
         <v>99</v>
       </c>
       <c r="B89" s="4">
-        <v>509.1756388888888</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4">
-        <v>418.69</v>
+        <v>250.06</v>
       </c>
       <c r="D89" s="4">
-        <v>316.01</v>
+        <v>208.58</v>
       </c>
       <c r="E89" s="4">
-        <v>509.1756388888888</v>
+        <v>0</v>
       </c>
       <c r="F89" s="4">
-        <v>2659.14</v>
+        <v>1750.42</v>
       </c>
       <c r="G89" s="4">
-        <v>316.01</v>
+        <v>208.58</v>
       </c>
       <c r="H89" s="4">
-        <v>3600.74</v>
+        <v>1460.06</v>
       </c>
       <c r="I89" s="4">
-        <v>2543.991541666667</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4">
-        <v>1958.13</v>
+        <v>1250.3</v>
       </c>
       <c r="K89" s="4">
-        <v>2343.32</v>
+        <v>1042.9</v>
       </c>
       <c r="L89" s="4">
-        <v>24783.18256944444</v>
+        <v>0</v>
       </c>
       <c r="M89" s="4">
-        <v>20176.61</v>
+        <v>16503.96</v>
       </c>
       <c r="N89" s="4">
-        <v>23179.03</v>
+        <v>13766.28</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4786,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="4">
-        <v>0</v>
+        <v>23192.44</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4794,43 +4785,43 @@
         <v>102</v>
       </c>
       <c r="B92" s="4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C92" s="4">
-        <v>250.06</v>
+        <v>0</v>
       </c>
       <c r="D92" s="4">
-        <v>208.58</v>
+        <v>0</v>
       </c>
       <c r="E92" s="4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F92" s="4">
-        <v>1750.42</v>
+        <v>0</v>
       </c>
       <c r="G92" s="4">
-        <v>208.58</v>
+        <v>0</v>
       </c>
       <c r="H92" s="4">
-        <v>1460.06</v>
+        <v>0</v>
       </c>
       <c r="I92" s="4">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="J92" s="4">
-        <v>1250.3</v>
+        <v>0</v>
       </c>
       <c r="K92" s="4">
-        <v>1042.9</v>
+        <v>0</v>
       </c>
       <c r="L92" s="4">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="M92" s="4">
-        <v>16503.96</v>
+        <v>0</v>
       </c>
       <c r="N92" s="4">
-        <v>13766.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4918,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="4">
-        <v>23192.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4929,40 +4920,40 @@
         <v>0</v>
       </c>
       <c r="C95" s="4">
-        <v>0</v>
+        <v>492.08</v>
       </c>
       <c r="D95" s="4">
-        <v>0</v>
+        <v>759.5</v>
       </c>
       <c r="E95" s="4">
         <v>0</v>
       </c>
       <c r="F95" s="4">
-        <v>0</v>
+        <v>4562.13</v>
       </c>
       <c r="G95" s="4">
-        <v>0</v>
+        <v>759.5</v>
       </c>
       <c r="H95" s="4">
-        <v>0</v>
+        <v>4058.3</v>
       </c>
       <c r="I95" s="4">
-        <v>0</v>
+        <v>373.3936666666666</v>
       </c>
       <c r="J95" s="4">
-        <v>0</v>
+        <v>3964.2</v>
       </c>
       <c r="K95" s="4">
-        <v>0</v>
+        <v>3328.39</v>
       </c>
       <c r="L95" s="4">
-        <v>0</v>
+        <v>1209.004458333333</v>
       </c>
       <c r="M95" s="4">
-        <v>0</v>
+        <v>25721.9</v>
       </c>
       <c r="N95" s="4">
-        <v>0</v>
+        <v>26305.28</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -5058,43 +5049,43 @@
         <v>108</v>
       </c>
       <c r="B98" s="4">
-        <v>758.1725555555556</v>
+        <v>0</v>
       </c>
       <c r="C98" s="4">
-        <v>492.08</v>
+        <v>440.77</v>
       </c>
       <c r="D98" s="4">
-        <v>759.5</v>
+        <v>414.04</v>
       </c>
       <c r="E98" s="4">
-        <v>758.1725555555556</v>
+        <v>0</v>
       </c>
       <c r="F98" s="4">
-        <v>4562.13</v>
+        <v>3391.84</v>
       </c>
       <c r="G98" s="4">
-        <v>759.5</v>
+        <v>414.04</v>
       </c>
       <c r="H98" s="4">
-        <v>4058.3</v>
+        <v>3124.43</v>
       </c>
       <c r="I98" s="4">
-        <v>5200.420638888889</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4">
-        <v>3964.2</v>
+        <v>2335.19</v>
       </c>
       <c r="K98" s="4">
-        <v>3328.39</v>
+        <v>4174.55</v>
       </c>
       <c r="L98" s="4">
-        <v>26832.76355555555</v>
+        <v>0</v>
       </c>
       <c r="M98" s="4">
-        <v>25721.9</v>
+        <v>27055.73</v>
       </c>
       <c r="N98" s="4">
-        <v>26305.28</v>
+        <v>27293.97</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -5190,43 +5181,43 @@
         <v>111</v>
       </c>
       <c r="B101" s="4">
-        <v>698.5564444444445</v>
+        <v>428.5555833333333</v>
       </c>
       <c r="C101" s="4">
-        <v>440.77</v>
+        <v>637.5700000000001</v>
       </c>
       <c r="D101" s="4">
-        <v>414.04</v>
+        <v>847.23</v>
       </c>
       <c r="E101" s="4">
-        <v>698.5564444444444</v>
+        <v>428.5555833333333</v>
       </c>
       <c r="F101" s="4">
-        <v>3391.84</v>
+        <v>6554.31</v>
       </c>
       <c r="G101" s="4">
-        <v>414.04</v>
+        <v>847.23</v>
       </c>
       <c r="H101" s="4">
-        <v>3124.43</v>
+        <v>6116.07</v>
       </c>
       <c r="I101" s="4">
-        <v>5175.097555555555</v>
+        <v>687.831875</v>
       </c>
       <c r="J101" s="4">
-        <v>2335.19</v>
+        <v>4896.54</v>
       </c>
       <c r="K101" s="4">
-        <v>4174.55</v>
+        <v>4253.3</v>
       </c>
       <c r="L101" s="4">
-        <v>38481.12379166666</v>
+        <v>4560.945124999999</v>
       </c>
       <c r="M101" s="4">
-        <v>27055.73</v>
+        <v>41389.75</v>
       </c>
       <c r="N101" s="4">
-        <v>27293.97</v>
+        <v>42419.71</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -5322,43 +5313,43 @@
         <v>114</v>
       </c>
       <c r="B104" s="4">
-        <v>1127.639708333333</v>
+        <v>0</v>
       </c>
       <c r="C104" s="4">
-        <v>637.5700000000001</v>
+        <v>637.7</v>
       </c>
       <c r="D104" s="4">
-        <v>847.23</v>
+        <v>963.75</v>
       </c>
       <c r="E104" s="4">
-        <v>1127.639708333333</v>
+        <v>0</v>
       </c>
       <c r="F104" s="4">
-        <v>6554.31</v>
+        <v>5004.43</v>
       </c>
       <c r="G104" s="4">
-        <v>847.23</v>
+        <v>963.75</v>
       </c>
       <c r="H104" s="4">
-        <v>6116.07</v>
+        <v>5643.7</v>
       </c>
       <c r="I104" s="4">
-        <v>5100.752041666666</v>
+        <v>28.01244444444444</v>
       </c>
       <c r="J104" s="4">
-        <v>4896.54</v>
+        <v>3825.77</v>
       </c>
       <c r="K104" s="4">
-        <v>4253.3</v>
+        <v>3657.01</v>
       </c>
       <c r="L104" s="4">
-        <v>49276.56594444448</v>
+        <v>314.5710694444444</v>
       </c>
       <c r="M104" s="4">
-        <v>41389.75</v>
+        <v>47067.92</v>
       </c>
       <c r="N104" s="4">
-        <v>42419.71</v>
+        <v>47284.18</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5454,43 +5445,43 @@
         <v>117</v>
       </c>
       <c r="B107" s="4">
-        <v>635.7658333333334</v>
+        <v>0</v>
       </c>
       <c r="C107" s="4">
-        <v>637.7</v>
+        <v>308.5</v>
       </c>
       <c r="D107" s="4">
-        <v>963.75</v>
+        <v>382.35</v>
       </c>
       <c r="E107" s="4">
-        <v>635.7658333333334</v>
+        <v>0</v>
       </c>
       <c r="F107" s="4">
-        <v>5004.43</v>
+        <v>2491.85</v>
       </c>
       <c r="G107" s="4">
-        <v>963.75</v>
+        <v>382.35</v>
       </c>
       <c r="H107" s="4">
-        <v>5643.7</v>
+        <v>2910.9</v>
       </c>
       <c r="I107" s="4">
-        <v>3895.95725</v>
+        <v>0</v>
       </c>
       <c r="J107" s="4">
-        <v>3825.77</v>
+        <v>1623.28</v>
       </c>
       <c r="K107" s="4">
-        <v>3657.01</v>
+        <v>1408.9</v>
       </c>
       <c r="L107" s="4">
-        <v>51546.97668055558</v>
+        <v>0</v>
       </c>
       <c r="M107" s="4">
-        <v>47067.92</v>
+        <v>20020.59</v>
       </c>
       <c r="N107" s="4">
-        <v>47284.18</v>
+        <v>19177.41</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5586,43 +5577,43 @@
         <v>120</v>
       </c>
       <c r="B110" s="4">
-        <v>321.0228333333333</v>
+        <v>0</v>
       </c>
       <c r="C110" s="4">
-        <v>308.5</v>
+        <v>0</v>
       </c>
       <c r="D110" s="4">
-        <v>382.35</v>
+        <v>0</v>
       </c>
       <c r="E110" s="4">
-        <v>321.0228333333333</v>
+        <v>0</v>
       </c>
       <c r="F110" s="4">
-        <v>2491.85</v>
+        <v>0</v>
       </c>
       <c r="G110" s="4">
-        <v>382.35</v>
+        <v>0</v>
       </c>
       <c r="H110" s="4">
-        <v>2910.9</v>
+        <v>180.8</v>
       </c>
       <c r="I110" s="4">
-        <v>2225.88395</v>
+        <v>33.552375</v>
       </c>
       <c r="J110" s="4">
-        <v>1623.28</v>
+        <v>0</v>
       </c>
       <c r="K110" s="4">
-        <v>1408.9</v>
+        <v>180.1</v>
       </c>
       <c r="L110" s="4">
-        <v>23765.05497222222</v>
+        <v>1422.012888888889</v>
       </c>
       <c r="M110" s="4">
-        <v>20020.59</v>
+        <v>0</v>
       </c>
       <c r="N110" s="4">
-        <v>19177.41</v>
+        <v>4180.4</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5721,40 +5712,40 @@
         <v>0</v>
       </c>
       <c r="C113" s="4">
-        <v>0</v>
+        <v>636.54</v>
       </c>
       <c r="D113" s="4">
-        <v>0</v>
+        <v>620.95</v>
       </c>
       <c r="E113" s="4">
         <v>0</v>
       </c>
       <c r="F113" s="4">
-        <v>0</v>
+        <v>4179.93</v>
       </c>
       <c r="G113" s="4">
-        <v>0</v>
+        <v>620.95</v>
       </c>
       <c r="H113" s="4">
-        <v>180.8</v>
+        <v>3757.2</v>
       </c>
       <c r="I113" s="4">
-        <v>33.552375</v>
+        <v>0</v>
       </c>
       <c r="J113" s="4">
-        <v>0</v>
+        <v>3017.19</v>
       </c>
       <c r="K113" s="4">
-        <v>180.1</v>
+        <v>2886.37</v>
       </c>
       <c r="L113" s="4">
-        <v>3071.948249999999</v>
+        <v>0</v>
       </c>
       <c r="M113" s="4">
-        <v>0</v>
+        <v>25745.79</v>
       </c>
       <c r="N113" s="4">
-        <v>4180.4</v>
+        <v>32408.53</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5850,43 +5841,43 @@
         <v>126</v>
       </c>
       <c r="B116" s="4">
-        <v>1336.174263888889</v>
+        <v>0</v>
       </c>
       <c r="C116" s="4">
-        <v>636.54</v>
+        <v>0</v>
       </c>
       <c r="D116" s="4">
-        <v>620.95</v>
+        <v>0</v>
       </c>
       <c r="E116" s="4">
-        <v>1336.174263888889</v>
+        <v>0</v>
       </c>
       <c r="F116" s="4">
-        <v>4179.93</v>
+        <v>0</v>
       </c>
       <c r="G116" s="4">
-        <v>620.95</v>
+        <v>0</v>
       </c>
       <c r="H116" s="4">
-        <v>3757.2</v>
+        <v>0</v>
       </c>
       <c r="I116" s="4">
-        <v>6231.976708333334</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4">
-        <v>3017.19</v>
+        <v>0</v>
       </c>
       <c r="K116" s="4">
-        <v>2886.37</v>
+        <v>0</v>
       </c>
       <c r="L116" s="4">
-        <v>48189.74796666665</v>
+        <v>0</v>
       </c>
       <c r="M116" s="4">
-        <v>25745.79</v>
+        <v>0</v>
       </c>
       <c r="N116" s="4">
-        <v>32408.53</v>
+        <v>3928.6</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5974,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="4">
-        <v>0</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5985,40 +5976,40 @@
         <v>0</v>
       </c>
       <c r="C119" s="4">
-        <v>0</v>
+        <v>587.05</v>
       </c>
       <c r="D119" s="4">
-        <v>0</v>
+        <v>302.2</v>
       </c>
       <c r="E119" s="4">
         <v>0</v>
       </c>
       <c r="F119" s="4">
-        <v>0</v>
+        <v>3557.35</v>
       </c>
       <c r="G119" s="4">
-        <v>0</v>
+        <v>302.2</v>
       </c>
       <c r="H119" s="4">
-        <v>0</v>
+        <v>3239.84</v>
       </c>
       <c r="I119" s="4">
         <v>0</v>
       </c>
       <c r="J119" s="4">
-        <v>0</v>
+        <v>2659.25</v>
       </c>
       <c r="K119" s="4">
-        <v>0</v>
+        <v>2034.41</v>
       </c>
       <c r="L119" s="4">
         <v>0</v>
       </c>
       <c r="M119" s="4">
-        <v>0</v>
+        <v>35169.3</v>
       </c>
       <c r="N119" s="4">
-        <v>3928.6</v>
+        <v>18334.41</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -6062,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="N120" s="5">
-        <v>0</v>
+        <v>481.4708508403361</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -6070,7 +6061,7 @@
         <v>131</v>
       </c>
       <c r="B121" s="4">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="C121" s="4">
         <v>0</v>
@@ -6079,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="4">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F121" s="4">
         <v>0</v>
@@ -6091,22 +6082,22 @@
         <v>0</v>
       </c>
       <c r="I121" s="4">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="J121" s="4">
         <v>0</v>
       </c>
       <c r="K121" s="4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L121" s="4">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="M121" s="4">
-        <v>0</v>
+        <v>99292</v>
       </c>
       <c r="N121" s="4">
-        <v>3808</v>
+        <v>21460.63</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -6114,43 +6105,43 @@
         <v>132</v>
       </c>
       <c r="B122" s="4">
-        <v>519.5188888888888</v>
+        <v>0</v>
       </c>
       <c r="C122" s="4">
-        <v>587.05</v>
+        <v>421.74</v>
       </c>
       <c r="D122" s="4">
-        <v>302.2</v>
+        <v>931.04</v>
       </c>
       <c r="E122" s="4">
-        <v>519.5188888888888</v>
+        <v>0</v>
       </c>
       <c r="F122" s="4">
-        <v>3557.35</v>
+        <v>4352.18</v>
       </c>
       <c r="G122" s="4">
-        <v>302.2</v>
+        <v>931.04</v>
       </c>
       <c r="H122" s="4">
-        <v>3239.84</v>
+        <v>6517.28</v>
       </c>
       <c r="I122" s="4">
-        <v>2444.146111111111</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4">
-        <v>2659.25</v>
+        <v>2808.7</v>
       </c>
       <c r="K122" s="4">
-        <v>2034.41</v>
+        <v>4655.2</v>
       </c>
       <c r="L122" s="4">
-        <v>38316.96595833333</v>
+        <v>0</v>
       </c>
       <c r="M122" s="4">
-        <v>35169.3</v>
+        <v>39034.84</v>
       </c>
       <c r="N122" s="4">
-        <v>18334.41</v>
+        <v>61448.64</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -6185,16 +6176,16 @@
         <v>0</v>
       </c>
       <c r="K123" s="5">
-        <v>0</v>
+        <v>5172.444444444444</v>
       </c>
       <c r="L123" s="5">
         <v>0</v>
       </c>
       <c r="M123" s="5">
-        <v>0</v>
+        <v>39.31317729525037</v>
       </c>
       <c r="N123" s="5">
-        <v>481.4708508403361</v>
+        <v>286.3319483165219</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -6202,7 +6193,7 @@
         <v>134</v>
       </c>
       <c r="B124" s="4">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="C124" s="4">
         <v>0</v>
@@ -6211,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="E124" s="4">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="F124" s="4">
         <v>0</v>
@@ -6223,22 +6214,22 @@
         <v>0</v>
       </c>
       <c r="I124" s="4">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="J124" s="4">
         <v>0</v>
       </c>
       <c r="K124" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L124" s="4">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="M124" s="4">
-        <v>99292</v>
+        <v>0</v>
       </c>
       <c r="N124" s="4">
-        <v>41550.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -6249,40 +6240,40 @@
         <v>0</v>
       </c>
       <c r="C125" s="4">
-        <v>421.74</v>
+        <v>980.3099999999999</v>
       </c>
       <c r="D125" s="4">
-        <v>931.04</v>
+        <v>787.0599999999999</v>
       </c>
       <c r="E125" s="4">
         <v>0</v>
       </c>
       <c r="F125" s="4">
-        <v>4352.18</v>
+        <v>6115.47</v>
       </c>
       <c r="G125" s="4">
-        <v>931.04</v>
+        <v>787.0599999999999</v>
       </c>
       <c r="H125" s="4">
-        <v>6517.28</v>
+        <v>5635.32</v>
       </c>
       <c r="I125" s="4">
         <v>0</v>
       </c>
       <c r="J125" s="4">
-        <v>2808.7</v>
+        <v>4221.15</v>
       </c>
       <c r="K125" s="4">
-        <v>4655.2</v>
+        <v>3619.1</v>
       </c>
       <c r="L125" s="4">
-        <v>17360</v>
+        <v>0</v>
       </c>
       <c r="M125" s="4">
-        <v>39034.84</v>
+        <v>57154.16</v>
       </c>
       <c r="N125" s="4">
-        <v>61448.64</v>
+        <v>49360.25</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6317,16 +6308,16 @@
         <v>0</v>
       </c>
       <c r="K126" s="5">
-        <v>2586.222222222222</v>
+        <v>0</v>
       </c>
       <c r="L126" s="5">
-        <v>4960000</v>
+        <v>0</v>
       </c>
       <c r="M126" s="5">
-        <v>39.31317729525037</v>
+        <v>0</v>
       </c>
       <c r="N126" s="5">
-        <v>147.8885879708683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6378,43 +6369,43 @@
         <v>138</v>
       </c>
       <c r="B128" s="4">
-        <v>796.3483333333334</v>
+        <v>0</v>
       </c>
       <c r="C128" s="4">
-        <v>980.3099999999999</v>
+        <v>846.78</v>
       </c>
       <c r="D128" s="4">
-        <v>787.0599999999999</v>
+        <v>824.1799999999999</v>
       </c>
       <c r="E128" s="4">
-        <v>796.3483333333334</v>
+        <v>0</v>
       </c>
       <c r="F128" s="4">
-        <v>6115.47</v>
+        <v>5927.46</v>
       </c>
       <c r="G128" s="4">
-        <v>787.0599999999999</v>
+        <v>824.1799999999999</v>
       </c>
       <c r="H128" s="4">
-        <v>5635.32</v>
+        <v>5769.26</v>
       </c>
       <c r="I128" s="4">
-        <v>4535.729777777778</v>
+        <v>0</v>
       </c>
       <c r="J128" s="4">
-        <v>4221.15</v>
+        <v>4233.9</v>
       </c>
       <c r="K128" s="4">
-        <v>3619.1</v>
+        <v>4120.9</v>
       </c>
       <c r="L128" s="4">
-        <v>58032.90601388889</v>
+        <v>0</v>
       </c>
       <c r="M128" s="4">
-        <v>57154.16</v>
+        <v>55887.48</v>
       </c>
       <c r="N128" s="4">
-        <v>49360.25</v>
+        <v>51648.38</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6510,43 +6501,43 @@
         <v>141</v>
       </c>
       <c r="B131" s="4">
-        <v>821.92</v>
+        <v>0</v>
       </c>
       <c r="C131" s="4">
-        <v>846.78</v>
+        <v>410.8</v>
       </c>
       <c r="D131" s="4">
-        <v>824.1799999999999</v>
+        <v>866.84</v>
       </c>
       <c r="E131" s="4">
-        <v>821.92</v>
+        <v>0</v>
       </c>
       <c r="F131" s="4">
-        <v>5927.46</v>
+        <v>3230.75</v>
       </c>
       <c r="G131" s="4">
-        <v>824.1799999999999</v>
+        <v>866.84</v>
       </c>
       <c r="H131" s="4">
-        <v>5769.26</v>
+        <v>3306.23</v>
       </c>
       <c r="I131" s="4">
-        <v>4109.6</v>
+        <v>0</v>
       </c>
       <c r="J131" s="4">
-        <v>4233.9</v>
+        <v>2474.44</v>
       </c>
       <c r="K131" s="4">
-        <v>4120.9</v>
+        <v>2065.32</v>
       </c>
       <c r="L131" s="4">
-        <v>54246.72</v>
+        <v>0</v>
       </c>
       <c r="M131" s="4">
-        <v>55887.48</v>
+        <v>30632.97</v>
       </c>
       <c r="N131" s="4">
-        <v>51648.38</v>
+        <v>34380.28</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6642,43 +6633,43 @@
         <v>144</v>
       </c>
       <c r="B134" s="4">
-        <v>573.6930555555555</v>
+        <v>0</v>
       </c>
       <c r="C134" s="4">
-        <v>410.8</v>
+        <v>144.38</v>
       </c>
       <c r="D134" s="4">
-        <v>866.84</v>
+        <v>208.58</v>
       </c>
       <c r="E134" s="4">
-        <v>573.6930555555555</v>
+        <v>0</v>
       </c>
       <c r="F134" s="4">
-        <v>3230.75</v>
+        <v>1010.66</v>
       </c>
       <c r="G134" s="4">
-        <v>866.84</v>
+        <v>208.58</v>
       </c>
       <c r="H134" s="4">
-        <v>3306.23</v>
+        <v>2104.64</v>
       </c>
       <c r="I134" s="4">
-        <v>2015.448055555556</v>
+        <v>0</v>
       </c>
       <c r="J134" s="4">
-        <v>2474.44</v>
+        <v>721.9</v>
       </c>
       <c r="K134" s="4">
-        <v>2065.32</v>
+        <v>1530.24</v>
       </c>
       <c r="L134" s="4">
-        <v>30139.51555555555</v>
+        <v>0</v>
       </c>
       <c r="M134" s="4">
-        <v>30632.97</v>
+        <v>9529.08</v>
       </c>
       <c r="N134" s="4">
-        <v>34380.28</v>
+        <v>18552.37</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -6774,43 +6765,43 @@
         <v>147</v>
       </c>
       <c r="B137" s="4">
-        <v>216.44</v>
+        <v>0</v>
       </c>
       <c r="C137" s="4">
-        <v>144.38</v>
+        <v>798.21</v>
       </c>
       <c r="D137" s="4">
-        <v>208.58</v>
+        <v>486.11</v>
       </c>
       <c r="E137" s="4">
-        <v>216.44</v>
+        <v>0</v>
       </c>
       <c r="F137" s="4">
-        <v>1010.66</v>
+        <v>4891.47</v>
       </c>
       <c r="G137" s="4">
-        <v>208.58</v>
+        <v>486.11</v>
       </c>
       <c r="H137" s="4">
-        <v>2104.64</v>
+        <v>4963.68</v>
       </c>
       <c r="I137" s="4">
-        <v>1082.2</v>
+        <v>0</v>
       </c>
       <c r="J137" s="4">
-        <v>721.9</v>
+        <v>3643.05</v>
       </c>
       <c r="K137" s="4">
-        <v>1530.24</v>
+        <v>3021.78</v>
       </c>
       <c r="L137" s="4">
-        <v>14600.82280555556</v>
+        <v>0</v>
       </c>
       <c r="M137" s="4">
-        <v>9529.08</v>
+        <v>44851.86</v>
       </c>
       <c r="N137" s="4">
-        <v>18552.37</v>
+        <v>44755.17</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -6906,43 +6897,43 @@
         <v>150</v>
       </c>
       <c r="B140" s="4">
-        <v>623.97</v>
+        <v>0</v>
       </c>
       <c r="C140" s="4">
-        <v>798.21</v>
+        <v>0</v>
       </c>
       <c r="D140" s="4">
-        <v>486.11</v>
+        <v>0</v>
       </c>
       <c r="E140" s="4">
-        <v>623.97</v>
+        <v>0</v>
       </c>
       <c r="F140" s="4">
-        <v>4891.47</v>
+        <v>0</v>
       </c>
       <c r="G140" s="4">
-        <v>486.11</v>
+        <v>0</v>
       </c>
       <c r="H140" s="4">
-        <v>4963.68</v>
+        <v>0</v>
       </c>
       <c r="I140" s="4">
-        <v>3119.85</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4">
-        <v>3643.05</v>
+        <v>0</v>
       </c>
       <c r="K140" s="4">
-        <v>3021.78</v>
+        <v>0</v>
       </c>
       <c r="L140" s="4">
-        <v>41182.02</v>
+        <v>0</v>
       </c>
       <c r="M140" s="4">
-        <v>44851.86</v>
+        <v>0</v>
       </c>
       <c r="N140" s="4">
-        <v>44755.17</v>
+        <v>220.41</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -7074,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="N143" s="4">
-        <v>220.41</v>
+        <v>183.48</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -7206,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="4">
-        <v>183.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -7332,13 +7323,13 @@
         <v>0</v>
       </c>
       <c r="L149" s="4">
-        <v>487.4147916666667</v>
+        <v>0</v>
       </c>
       <c r="M149" s="4">
         <v>0</v>
       </c>
       <c r="N149" s="4">
-        <v>0</v>
+        <v>659.24</v>
       </c>
     </row>
     <row r="150" spans="1:14">
@@ -7440,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="D152" s="4">
-        <v>0</v>
+        <v>194.65</v>
       </c>
       <c r="E152" s="4">
         <v>0</v>
@@ -7449,10 +7440,10 @@
         <v>0</v>
       </c>
       <c r="G152" s="4">
-        <v>0</v>
+        <v>194.65</v>
       </c>
       <c r="H152" s="4">
-        <v>0</v>
+        <v>1160.53</v>
       </c>
       <c r="I152" s="4">
         <v>0</v>
@@ -7461,16 +7452,16 @@
         <v>0</v>
       </c>
       <c r="K152" s="4">
-        <v>0</v>
+        <v>208.97</v>
       </c>
       <c r="L152" s="4">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="M152" s="4">
         <v>0</v>
       </c>
       <c r="N152" s="4">
-        <v>659.24</v>
+        <v>6727.23</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -7572,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="D155" s="4">
-        <v>194.65</v>
+        <v>0</v>
       </c>
       <c r="E155" s="4">
         <v>0</v>
@@ -7581,10 +7572,10 @@
         <v>0</v>
       </c>
       <c r="G155" s="4">
-        <v>194.65</v>
+        <v>0</v>
       </c>
       <c r="H155" s="4">
-        <v>1160.53</v>
+        <v>0</v>
       </c>
       <c r="I155" s="4">
         <v>0</v>
@@ -7593,16 +7584,16 @@
         <v>0</v>
       </c>
       <c r="K155" s="4">
-        <v>208.97</v>
+        <v>0</v>
       </c>
       <c r="L155" s="4">
-        <v>554.7129833333333</v>
+        <v>0</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>
       </c>
       <c r="N155" s="4">
-        <v>6727.23</v>
+        <v>217.86</v>
       </c>
     </row>
     <row r="156" spans="1:14">
@@ -7728,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="L158" s="4">
-        <v>2898.262472222222</v>
+        <v>0</v>
       </c>
       <c r="M158" s="4">
         <v>0</v>
       </c>
       <c r="N158" s="4">
-        <v>217.86</v>
+        <v>186.27</v>
       </c>
     </row>
     <row r="159" spans="1:14">
@@ -7860,13 +7851,13 @@
         <v>0</v>
       </c>
       <c r="L161" s="4">
-        <v>106.4046527777778</v>
+        <v>0</v>
       </c>
       <c r="M161" s="4">
         <v>0</v>
       </c>
       <c r="N161" s="4">
-        <v>186.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:14">
@@ -7992,13 +7983,13 @@
         <v>0</v>
       </c>
       <c r="L164" s="4">
-        <v>216.6333333333334</v>
+        <v>0</v>
       </c>
       <c r="M164" s="4">
         <v>0</v>
       </c>
       <c r="N164" s="4">
-        <v>0</v>
+        <v>7781</v>
       </c>
     </row>
     <row r="165" spans="1:14">
@@ -8130,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="N167" s="4">
-        <v>7781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:14">
@@ -8256,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="4">
-        <v>1207.070888888889</v>
+        <v>0</v>
       </c>
       <c r="M170" s="4">
         <v>0</v>
@@ -8309,136 +8300,136 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
-      <c r="A172" s="2" t="s">
+    <row r="174" spans="1:14">
+      <c r="A174" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B172" s="4">
-        <v>0</v>
-      </c>
-      <c r="C172" s="4">
-        <v>0</v>
-      </c>
-      <c r="D172" s="4">
-        <v>0</v>
-      </c>
-      <c r="E172" s="4">
-        <v>0</v>
-      </c>
-      <c r="F172" s="4">
-        <v>0</v>
-      </c>
-      <c r="G172" s="4">
-        <v>0</v>
-      </c>
-      <c r="H172" s="4">
-        <v>0</v>
-      </c>
-      <c r="I172" s="4">
-        <v>0</v>
-      </c>
-      <c r="J172" s="4">
-        <v>0</v>
-      </c>
-      <c r="K172" s="4">
-        <v>0</v>
-      </c>
-      <c r="L172" s="4">
-        <v>0</v>
-      </c>
-      <c r="M172" s="4">
-        <v>0</v>
-      </c>
-      <c r="N172" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14">
-      <c r="A173" s="2" t="s">
+      <c r="B174" s="4">
+        <v>226541.79</v>
+      </c>
+      <c r="C174" s="4">
+        <v>221676.86</v>
+      </c>
+      <c r="D174" s="4">
+        <v>53747.7</v>
+      </c>
+      <c r="E174" s="4">
+        <v>226541.79</v>
+      </c>
+      <c r="F174" s="4">
+        <v>2033575.15</v>
+      </c>
+      <c r="G174" s="4">
+        <v>53747.7</v>
+      </c>
+      <c r="H174" s="4">
+        <v>757383.74</v>
+      </c>
+      <c r="I174" s="4">
+        <v>1612574.68</v>
+      </c>
+      <c r="J174" s="4">
+        <v>1691712.47</v>
+      </c>
+      <c r="K174" s="4">
+        <v>1055474.51</v>
+      </c>
+      <c r="L174" s="4">
+        <v>9340367.379999999</v>
+      </c>
+      <c r="M174" s="4">
+        <v>9866359.959999997</v>
+      </c>
+      <c r="N174" s="4">
+        <v>4704609</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="A175" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B173" s="4">
-        <v>0</v>
-      </c>
-      <c r="C173" s="4">
-        <v>0</v>
-      </c>
-      <c r="D173" s="4">
-        <v>0</v>
-      </c>
-      <c r="E173" s="4">
-        <v>0</v>
-      </c>
-      <c r="F173" s="4">
-        <v>0</v>
-      </c>
-      <c r="G173" s="4">
-        <v>0</v>
-      </c>
-      <c r="H173" s="4">
-        <v>0</v>
-      </c>
-      <c r="I173" s="4">
-        <v>0</v>
-      </c>
-      <c r="J173" s="4">
-        <v>0</v>
-      </c>
-      <c r="K173" s="4">
-        <v>0</v>
-      </c>
-      <c r="L173" s="4">
-        <v>24.909</v>
-      </c>
-      <c r="M173" s="4">
-        <v>0</v>
-      </c>
-      <c r="N173" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14">
-      <c r="A174" s="2" t="s">
+      <c r="B175" s="4">
+        <v>1640.620861111111</v>
+      </c>
+      <c r="C175" s="4">
+        <v>40852.59999999999</v>
+      </c>
+      <c r="D175" s="4">
+        <v>41105.27999999999</v>
+      </c>
+      <c r="E175" s="4">
+        <v>1640.620861111111</v>
+      </c>
+      <c r="F175" s="4">
+        <v>310103.1299999999</v>
+      </c>
+      <c r="G175" s="4">
+        <v>41105.27999999999</v>
+      </c>
+      <c r="H175" s="4">
+        <v>284515.6</v>
+      </c>
+      <c r="I175" s="4">
+        <v>8372.552705555556</v>
+      </c>
+      <c r="J175" s="4">
+        <v>218361.7</v>
+      </c>
+      <c r="K175" s="4">
+        <v>286798.2999999999</v>
+      </c>
+      <c r="L175" s="4">
+        <v>81789.57724444444</v>
+      </c>
+      <c r="M175" s="4">
+        <v>2096491.230000001</v>
+      </c>
+      <c r="N175" s="4">
+        <v>2335238.84</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
+      <c r="A176" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B174" s="5">
-        <v>0</v>
-      </c>
-      <c r="C174" s="5">
-        <v>0</v>
-      </c>
-      <c r="D174" s="5">
-        <v>0</v>
-      </c>
-      <c r="E174" s="5">
-        <v>0</v>
-      </c>
-      <c r="F174" s="5">
-        <v>0</v>
-      </c>
-      <c r="G174" s="5">
-        <v>0</v>
-      </c>
-      <c r="H174" s="5">
-        <v>0</v>
-      </c>
-      <c r="I174" s="5">
-        <v>0</v>
-      </c>
-      <c r="J174" s="5">
-        <v>0</v>
-      </c>
-      <c r="K174" s="5">
-        <v>0</v>
-      </c>
-      <c r="L174" s="5">
-        <v>0</v>
-      </c>
-      <c r="M174" s="5">
-        <v>0</v>
-      </c>
-      <c r="N174" s="5">
-        <v>0</v>
+      <c r="B176" s="5">
+        <v>0.724202303297379</v>
+      </c>
+      <c r="C176" s="5">
+        <v>18.42889690877072</v>
+      </c>
+      <c r="D176" s="5">
+        <v>76.47821209093595</v>
+      </c>
+      <c r="E176" s="5">
+        <v>0.724202303297379</v>
+      </c>
+      <c r="F176" s="5">
+        <v>15.24916008144572</v>
+      </c>
+      <c r="G176" s="5">
+        <v>76.47821209093595</v>
+      </c>
+      <c r="H176" s="5">
+        <v>37.56558069229212</v>
+      </c>
+      <c r="I176" s="5">
+        <v>0.5192040287743793</v>
+      </c>
+      <c r="J176" s="5">
+        <v>12.90773130022503</v>
+      </c>
+      <c r="K176" s="5">
+        <v>27.17245156398897</v>
+      </c>
+      <c r="L176" s="5">
+        <v>0.8756569620545746</v>
+      </c>
+      <c r="M176" s="5">
+        <v>21.24888245005812</v>
+      </c>
+      <c r="N176" s="5">
+        <v>49.63725657116245</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -8446,175 +8437,43 @@
         <v>185</v>
       </c>
       <c r="B177" s="4">
-        <v>226520.24</v>
+        <v>224901.1691388889</v>
       </c>
       <c r="C177" s="4">
-        <v>221676.86</v>
+        <v>180824.26</v>
       </c>
       <c r="D177" s="4">
-        <v>321194.04</v>
+        <v>12642.42000000001</v>
       </c>
       <c r="E177" s="4">
-        <v>226520.24</v>
+        <v>224901.1691388889</v>
       </c>
       <c r="F177" s="4">
-        <v>2033575.15</v>
+        <v>1723472.02</v>
       </c>
       <c r="G177" s="4">
-        <v>321194.04</v>
+        <v>12642.42000000001</v>
       </c>
       <c r="H177" s="4">
-        <v>1967404.91</v>
+        <v>472868.14</v>
       </c>
       <c r="I177" s="4">
-        <v>1612553.13</v>
+        <v>1604202.127294444</v>
       </c>
       <c r="J177" s="4">
-        <v>1691712.47</v>
+        <v>1473350.77</v>
       </c>
       <c r="K177" s="4">
-        <v>1915123.54</v>
+        <v>768676.2100000001</v>
       </c>
       <c r="L177" s="4">
-        <v>9340345.829999998</v>
+        <v>9258577.802755555</v>
       </c>
       <c r="M177" s="4">
-        <v>9866359.959999997</v>
+        <v>7769868.729999997</v>
       </c>
       <c r="N177" s="4">
-        <v>11673883.46</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14">
-      <c r="A178" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B178" s="4">
-        <v>36987.27695833333</v>
-      </c>
-      <c r="C178" s="4">
-        <v>40852.59999999999</v>
-      </c>
-      <c r="D178" s="4">
-        <v>41105.27999999999</v>
-      </c>
-      <c r="E178" s="4">
-        <v>36987.27695833333</v>
-      </c>
-      <c r="F178" s="4">
-        <v>310103.1299999999</v>
-      </c>
-      <c r="G178" s="4">
-        <v>41105.27999999999</v>
-      </c>
-      <c r="H178" s="4">
-        <v>284515.6</v>
-      </c>
-      <c r="I178" s="4">
-        <v>207858.4766138889</v>
-      </c>
-      <c r="J178" s="4">
-        <v>218361.7</v>
-      </c>
-      <c r="K178" s="4">
-        <v>286798.2999999999</v>
-      </c>
-      <c r="L178" s="4">
-        <v>2346381.640930555</v>
-      </c>
-      <c r="M178" s="4">
-        <v>2096491.230000001</v>
-      </c>
-      <c r="N178" s="4">
-        <v>2335238.84</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14">
-      <c r="A179" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B179" s="5">
-        <v>16.32846449320967</v>
-      </c>
-      <c r="C179" s="5">
-        <v>18.42889690877072</v>
-      </c>
-      <c r="D179" s="5">
-        <v>12.7976471792565</v>
-      </c>
-      <c r="E179" s="5">
-        <v>16.32846449320967</v>
-      </c>
-      <c r="F179" s="5">
-        <v>15.24916008144572</v>
-      </c>
-      <c r="G179" s="5">
-        <v>12.7976471792565</v>
-      </c>
-      <c r="H179" s="5">
-        <v>14.46146639941038</v>
-      </c>
-      <c r="I179" s="5">
-        <v>12.89002345081733</v>
-      </c>
-      <c r="J179" s="5">
-        <v>12.90773130022503</v>
-      </c>
-      <c r="K179" s="5">
-        <v>14.97544644038995</v>
-      </c>
-      <c r="L179" s="5">
-        <v>25.12092896383212</v>
-      </c>
-      <c r="M179" s="5">
-        <v>21.24888245005812</v>
-      </c>
-      <c r="N179" s="5">
-        <v>20.00395881971568</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14">
-      <c r="A180" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B180" s="4">
-        <v>189532.9630416666</v>
-      </c>
-      <c r="C180" s="4">
-        <v>180824.26</v>
-      </c>
-      <c r="D180" s="4">
-        <v>280088.76</v>
-      </c>
-      <c r="E180" s="4">
-        <v>189532.9630416666</v>
-      </c>
-      <c r="F180" s="4">
-        <v>1723472.02</v>
-      </c>
-      <c r="G180" s="4">
-        <v>280088.76</v>
-      </c>
-      <c r="H180" s="4">
-        <v>1682889.31</v>
-      </c>
-      <c r="I180" s="4">
-        <v>1404694.653386111</v>
-      </c>
-      <c r="J180" s="4">
-        <v>1473350.77</v>
-      </c>
-      <c r="K180" s="4">
-        <v>1628325.24</v>
-      </c>
-      <c r="L180" s="4">
-        <v>6993964.189069442</v>
-      </c>
-      <c r="M180" s="4">
-        <v>7769868.729999997</v>
-      </c>
-      <c r="N180" s="4">
-        <v>9338644.619999997</v>
+        <v>2369370.16</v>
       </c>
     </row>
   </sheetData>
